--- a/results/onxxgawftv.xlsx
+++ b/results/onxxgawftv.xlsx
@@ -72,7 +72,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -443,18 +443,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I132"/>
+  <dimension ref="A1:K131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -475,37 +477,75 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Subject 1</t>
+          <t>Assamese</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Subject 2</t>
+          <t>English</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Subject 3</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Subject 4</t>
+          <t>Art &amp; Craft</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Subject 5</t>
+          <t>EVS</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Subject 6</t>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Science</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Social Science</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Ankur</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Rituparna Nath</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -514,25 +554,29 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Rituparna Nath</t>
+          <t>Kaushik Boro</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>70</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -541,25 +585,29 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Kaushik Boro</t>
+          <t>Pallabi Bora</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>64</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -568,25 +616,29 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Pallabi Bora</t>
+          <t>Chayan Deka</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>34</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -595,25 +647,29 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Chayan Deka</t>
+          <t>Sourav Sarmah</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>37</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -622,25 +678,29 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Sourav Sarmah</t>
+          <t>Barnali Hazarika</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>49</v>
+        <v>97</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>83</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -649,25 +709,29 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Barnali Hazarika</t>
+          <t>Sourav Sharma</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>34</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -676,25 +740,29 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Sourav Sharma</t>
+          <t>Rima Baruah</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>86</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -703,25 +771,29 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Rima Baruah</t>
+          <t>Bikash Bora</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>76</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -730,52 +802,60 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Bikash Bora</t>
+          <t>Kangkan Dutta</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>53</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Ankur</t>
+          <t>Mukul</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Kangkan Dutta</t>
+          <t>Nirupama Boro</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>47</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -784,25 +864,29 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nirupama Boro</t>
+          <t>Himangshu Kakati</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>43</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -811,25 +895,29 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Himangshu Kakati</t>
+          <t>Aarav Bhattacharya</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>61</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -838,25 +926,29 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Aarav Bhattacharya</t>
+          <t>Chayan Saikia</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>36</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -865,25 +957,29 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Chayan Saikia</t>
+          <t>Sangita Mahanta</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>94</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -892,25 +988,29 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Sangita Mahanta</t>
+          <t>Rahul Hazarika</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>43</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -919,25 +1019,29 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Rahul Hazarika</t>
+          <t>Rupam Baruah</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>71</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -946,25 +1050,29 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Rupam Baruah</t>
+          <t>Dimpi Das</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="G19" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="E19" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>44</v>
-      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -973,25 +1081,29 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Dimpi Das</t>
+          <t>Chayan Sarmah</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>90</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1000,52 +1112,60 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Chayan Sarmah</t>
+          <t>Bikash Rabha</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>97</v>
+        <v>46</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>53</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Mukul</t>
+          <t>Prabhat</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Bikash Rabha</t>
+          <t>Rituparna Bhattacharya</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>35</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1054,25 +1174,29 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Rituparna Bhattacharya</t>
+          <t>Rahul Saikia</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>70</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1081,25 +1205,29 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Rahul Saikia</t>
+          <t>Sumi Deka</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>52</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1108,25 +1236,29 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Sumi Deka</t>
+          <t>Chayan Boro</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>68</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1135,25 +1267,29 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Chayan Boro</t>
+          <t>Utpal Rabha</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>61</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1162,25 +1298,29 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Utpal Rabha</t>
+          <t>Anaya Mahanta</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>70</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1189,25 +1329,29 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Anaya Mahanta</t>
+          <t>Karabi Nath</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>87</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1216,25 +1360,29 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Karabi Nath</t>
+          <t>Barnali Boro</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>52</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1243,25 +1391,29 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Barnali Boro</t>
+          <t>Karabi Deka</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>64</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1270,52 +1422,62 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Karabi Deka</t>
+          <t>Kangkan Boro</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>19</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Prabhat</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Kangkan Boro</t>
+          <t>Dipankar Saikia</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>39</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1324,28 +1486,31 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Dipankar Saikia</t>
+          <t>Mamoni Choudhury</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="E33" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>90</v>
-      </c>
+      <c r="I33" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1354,28 +1519,31 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Mamoni Choudhury</t>
+          <t>Dipankar Baruah</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>59</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="3" t="n">
-        <v>65</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1384,28 +1552,31 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Dipankar Baruah</t>
+          <t>Mitali Nath</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>62</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="3" t="n">
-        <v>48</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1414,28 +1585,31 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Mitali Nath</t>
+          <t>Anaya Hazarika</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>58</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="3" t="n">
-        <v>89</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1444,28 +1618,31 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Anaya Hazarika</t>
+          <t>Rahul Kalita</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>61</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="3" t="n">
-        <v>37</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1474,28 +1651,31 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Rahul Kalita</t>
+          <t>Kaushik Deka</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>86</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="3" t="n">
-        <v>62</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1504,28 +1684,31 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Kaushik Deka</t>
+          <t>Mamoni Sarmah</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>47</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="3" t="n">
-        <v>94</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1534,28 +1717,31 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Mamoni Sarmah</t>
+          <t>Rupam Kakati</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>70</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="3" t="n">
-        <v>56</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1564,58 +1750,64 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Rupam Kakati</t>
+          <t>Sangita Deka</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>91</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="3" t="n">
-        <v>34</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Sangita Deka</t>
+          <t>Anaya Saikia</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>98</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="3" t="n">
         <v>43</v>
       </c>
+      <c r="I42" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1624,28 +1816,31 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Anaya Saikia</t>
+          <t>Pranjal Rabha</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>43</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="3" t="n">
-        <v>78</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1654,28 +1849,31 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Pranjal Rabha</t>
+          <t>Juri Bora</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>77</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="3" t="n">
-        <v>71</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1684,28 +1882,31 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Juri Bora</t>
+          <t>Ankita Sarmah</t>
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="E45" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="F45" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>58</v>
-      </c>
+      <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="3" t="n">
-        <v>46</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1714,28 +1915,31 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Ankita Sarmah</t>
+          <t>Jyotirmoy Das</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>75</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="3" t="n">
-        <v>43</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1744,28 +1948,31 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Jyotirmoy Das</t>
+          <t>Kaushik Gogoi</t>
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>72</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="3" t="n">
-        <v>53</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1774,28 +1981,31 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Kaushik Gogoi</t>
+          <t>Gitika Bora</t>
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>57</v>
-      </c>
-      <c r="G48" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="I48" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="H48" s="3" t="n">
-        <v>36</v>
-      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1804,28 +2014,31 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Gitika Bora</t>
+          <t>Nayan Medhi</t>
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="G49" s="3" t="n">
-        <v>52</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="3" t="n">
-        <v>49</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1834,28 +2047,31 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Nayan Medhi</t>
+          <t>Pooja Das</t>
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>74</v>
-      </c>
-      <c r="G50" s="3" t="n">
-        <v>44</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="3" t="n">
-        <v>43</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1864,58 +2080,64 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Pooja Das</t>
+          <t>Rahul Sharma</t>
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>71</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="3" t="n">
-        <v>83</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Class 3</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Rahul Sharma</t>
+          <t>Sourav Kalita</t>
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="G52" s="3" t="n">
-        <v>59</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="3" t="n">
-        <v>60</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1924,28 +2146,31 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Sourav Kalita</t>
+          <t>Nayan Kakati</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="G53" s="3" t="n">
-        <v>55</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="3" t="n">
-        <v>49</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1954,28 +2179,31 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Nayan Kakati</t>
+          <t>Mintu Kakati</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="G54" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="H54" s="3" t="n">
-        <v>94</v>
-      </c>
+      <c r="I54" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -1984,28 +2212,31 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Mintu Kakati</t>
+          <t>Rima Choudhury</t>
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="G55" s="3" t="n">
-        <v>83</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="3" t="n">
-        <v>34</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="I55" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2014,28 +2245,31 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Rima Choudhury</t>
+          <t>Utpal Medhi</t>
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>67</v>
-      </c>
-      <c r="G56" s="3" t="n">
-        <v>79</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="3" t="n">
-        <v>77</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2044,28 +2278,31 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Utpal Medhi</t>
+          <t>Partha Boro</t>
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="G57" s="3" t="n">
-        <v>53</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="3" t="n">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2074,28 +2311,31 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Partha Boro</t>
+          <t>Nirupama Kalita</t>
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="G58" s="3" t="n">
-        <v>70</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="3" t="n">
-        <v>85</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2104,28 +2344,31 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Nirupama Kalita</t>
+          <t>Mintu Sharma</t>
         </is>
       </c>
       <c r="D59" s="3" t="n">
         <v>66</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="F59" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="G59" s="3" t="n">
-        <v>78</v>
-      </c>
-      <c r="H59" s="3" t="n">
-        <v>54</v>
-      </c>
+      <c r="I59" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2134,28 +2377,31 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Mintu Sharma</t>
+          <t>Dipankar Choudhury</t>
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="G60" s="3" t="n">
-        <v>35</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="3" t="n">
-        <v>97</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2164,58 +2410,64 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Dipankar Choudhury</t>
+          <t>Priya Sarmah</t>
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E61" s="3" t="n">
         <v>62</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="G61" s="3" t="n">
-        <v>37</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="I61" s="3" t="n">
         <v>91</v>
       </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Class 3</t>
+          <t>Class 4</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Priya Sarmah</t>
+          <t>Rimjim Kakati</t>
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="F62" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="G62" s="3" t="n">
-        <v>84</v>
-      </c>
+      <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="3" t="n">
-        <v>91</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2224,28 +2476,31 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Rimjim Kakati</t>
+          <t>Sourav Choudhury</t>
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="G63" s="3" t="n">
-        <v>59</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="3" t="n">
-        <v>79</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2254,28 +2509,31 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Sourav Choudhury</t>
+          <t>Karabi Sarmah</t>
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="G64" s="3" t="n">
-        <v>93</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="3" t="n">
-        <v>91</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2284,28 +2542,31 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Karabi Sarmah</t>
+          <t>Kaushik Mahanta</t>
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="E65" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="F65" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="G65" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="H65" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="I65" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2314,28 +2575,31 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Kaushik Mahanta</t>
+          <t>Nirupama Gogoi</t>
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="G66" s="3" t="n">
-        <v>52</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="3" t="n">
-        <v>94</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2344,28 +2608,31 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Nirupama Gogoi</t>
+          <t>Aarav Kakati</t>
         </is>
       </c>
       <c r="D67" s="3" t="n">
         <v>56</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="G67" s="3" t="n">
-        <v>85</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="3" t="n">
-        <v>59</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -2374,28 +2641,31 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Aarav Kakati</t>
+          <t>Rimjim Bora</t>
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="G68" s="3" t="n">
-        <v>43</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="3" t="n">
-        <v>52</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2404,28 +2674,31 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Rimjim Bora</t>
+          <t>Sourav Bora</t>
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="G69" s="3" t="n">
-        <v>37</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="3" t="n">
-        <v>79</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2434,28 +2707,31 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Sourav Bora</t>
+          <t>Kaushik Bhattacharya</t>
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="G70" s="3" t="n">
-        <v>96</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="3" t="n">
-        <v>48</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="I70" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -2464,58 +2740,64 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Kaushik Bhattacharya</t>
+          <t>Sumi Kakati</t>
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="G71" s="3" t="n">
-        <v>83</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="3" t="n">
-        <v>53</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Class 4</t>
+          <t>Class 5</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Sumi Kakati</t>
+          <t>Nayan Hazarika</t>
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="G72" s="3" t="n">
-        <v>88</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="I72" s="3" t="n">
         <v>64</v>
       </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -2524,28 +2806,31 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Nayan Hazarika</t>
+          <t>Himangshu Rabha</t>
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="G73" s="3" t="n">
-        <v>59</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="3" t="n">
-        <v>64</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="I73" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -2554,28 +2839,31 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Himangshu Rabha</t>
+          <t>Jyotirmoy Kakati</t>
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="G74" s="3" t="n">
-        <v>82</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="3" t="n">
-        <v>35</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="I74" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -2584,28 +2872,31 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Jyotirmoy Kakati</t>
+          <t>Barnali Kakati</t>
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="G75" s="3" t="n">
-        <v>49</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="3" t="n">
-        <v>39</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="I75" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2614,28 +2905,31 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Barnali Kakati</t>
+          <t>Mamoni Rabha</t>
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E76" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="F76" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="F76" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="G76" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="3" t="n">
-        <v>67</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2644,28 +2938,31 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Mamoni Rabha</t>
+          <t>Sumi Gogoi</t>
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="G77" s="3" t="n">
-        <v>44</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="3" t="n">
-        <v>89</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -2674,28 +2971,31 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Sumi Gogoi</t>
+          <t>Rimjim Hazarika</t>
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="G78" s="3" t="n">
-        <v>92</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="3" t="n">
-        <v>49</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -2704,28 +3004,31 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Rimjim Hazarika</t>
+          <t>Dimpi Mahanta</t>
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="G79" s="3" t="n">
-        <v>40</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="3" t="n">
-        <v>51</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -2734,28 +3037,31 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Dimpi Mahanta</t>
+          <t>Jyotirmoy Bora</t>
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="G80" s="3" t="n">
-        <v>39</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="3" t="n">
-        <v>35</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -2764,57 +3070,65 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Jyotirmoy Bora</t>
+          <t>Juri Boro</t>
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="G81" s="3" t="n">
-        <v>94</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="3" t="n">
-        <v>61</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Class 5</t>
+          <t>Class 6</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Juri Boro</t>
+          <t>Gitika Baruah</t>
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="G82" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="H82" s="3" t="n">
-        <v>42</v>
+        <v>53</v>
+      </c>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="K82" s="3" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="83">
@@ -2824,30 +3138,32 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Gitika Baruah</t>
+          <t>Rituparna Mahanta</t>
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="E83" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="F83" s="3" t="n">
         <v>95</v>
       </c>
-      <c r="F83" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="G83" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="H83" s="3" t="n">
-        <v>35</v>
-      </c>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr"/>
       <c r="I83" s="3" t="n">
-        <v>75</v>
+        <v>91</v>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="K83" s="3" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="84">
@@ -2857,30 +3173,32 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Rituparna Mahanta</t>
+          <t>Mintu Sarmah</t>
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="G84" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="H84" s="3" t="n">
-        <v>62</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="3" t="n">
-        <v>91</v>
+        <v>60</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="K84" s="3" t="n">
+        <v>77</v>
       </c>
     </row>
     <row r="85">
@@ -2890,30 +3208,32 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Mintu Sarmah</t>
+          <t>Bikash Hazarika</t>
         </is>
       </c>
       <c r="D85" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="E85" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="E85" s="3" t="n">
-        <v>54</v>
-      </c>
       <c r="F85" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="G85" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H85" s="3" t="n">
-        <v>77</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="3" t="n">
-        <v>60</v>
+        <v>69</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="K85" s="3" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="86">
@@ -2923,30 +3243,32 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Bikash Hazarika</t>
+          <t>Rahul Choudhury</t>
         </is>
       </c>
       <c r="D86" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="E86" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="E86" s="3" t="n">
-        <v>52</v>
-      </c>
       <c r="F86" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="G86" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="H86" s="3" t="n">
-        <v>51</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="3" t="n">
-        <v>69</v>
+        <v>65</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="K86" s="3" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="87">
@@ -2956,30 +3278,32 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Rahul Choudhury</t>
+          <t>Sumi Sarmah</t>
         </is>
       </c>
       <c r="D87" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="J87" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="E87" s="3" t="n">
-        <v>77</v>
-      </c>
-      <c r="F87" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="G87" s="3" t="n">
-        <v>77</v>
-      </c>
-      <c r="H87" s="3" t="n">
+      <c r="K87" s="3" t="n">
         <v>56</v>
-      </c>
-      <c r="I87" s="3" t="n">
-        <v>65</v>
       </c>
     </row>
     <row r="88">
@@ -2989,30 +3313,32 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Sumi Sarmah</t>
+          <t>Sumi Kalita</t>
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="G88" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="H88" s="3" t="n">
-        <v>56</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="3" t="n">
-        <v>78</v>
+        <v>87</v>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="K88" s="3" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="89">
@@ -3022,30 +3348,32 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Sumi Kalita</t>
+          <t>Priya Rabha</t>
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>86</v>
-      </c>
-      <c r="G89" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="H89" s="3" t="n">
-        <v>36</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr"/>
       <c r="I89" s="3" t="n">
-        <v>87</v>
+        <v>81</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="K89" s="3" t="n">
+        <v>57</v>
       </c>
     </row>
     <row r="90">
@@ -3055,30 +3383,32 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Priya Rabha</t>
+          <t>Sumi Dutta</t>
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="G90" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="H90" s="3" t="n">
-        <v>57</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr"/>
       <c r="I90" s="3" t="n">
-        <v>81</v>
+        <v>86</v>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="K90" s="3" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="91">
@@ -3088,63 +3418,67 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Sumi Dutta</t>
+          <t>Rupam Gogoi</t>
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="G91" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="H91" s="3" t="n">
-        <v>71</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr"/>
       <c r="I91" s="3" t="n">
-        <v>86</v>
+        <v>92</v>
+      </c>
+      <c r="J91" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="K91" s="3" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Class 6</t>
+          <t>Class 7</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Rupam Gogoi</t>
+          <t>Kasturi Rabha</t>
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="F92" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="G92" s="3" t="n">
-        <v>57</v>
-      </c>
-      <c r="H92" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="I92" s="3" t="n">
-        <v>92</v>
+      <c r="J92" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="K92" s="3" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="93">
@@ -3154,29 +3488,31 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Kasturi Rabha</t>
+          <t>Ankita Saikia</t>
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="G93" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="H93" s="3" t="n">
-        <v>90</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr"/>
       <c r="I93" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="J93" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="K93" s="3" t="n">
         <v>78</v>
       </c>
     </row>
@@ -3187,30 +3523,32 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Ankita Saikia</t>
+          <t>Hirak Kakati</t>
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>78</v>
-      </c>
-      <c r="G94" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="H94" s="3" t="n">
-        <v>78</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr"/>
       <c r="I94" s="3" t="n">
-        <v>58</v>
+        <v>95</v>
+      </c>
+      <c r="J94" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="K94" s="3" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="95">
@@ -3220,30 +3558,32 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Hirak Kakati</t>
+          <t>Chayan Bhattacharya</t>
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="G95" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="H95" s="3" t="n">
-        <v>46</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr"/>
       <c r="I95" s="3" t="n">
-        <v>95</v>
+        <v>77</v>
+      </c>
+      <c r="J95" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="K95" s="3" t="n">
+        <v>93</v>
       </c>
     </row>
     <row r="96">
@@ -3253,30 +3593,32 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Chayan Bhattacharya</t>
+          <t>Nayan Choudhury</t>
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="G96" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="H96" s="3" t="n">
-        <v>93</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr"/>
       <c r="I96" s="3" t="n">
-        <v>77</v>
+        <v>86</v>
+      </c>
+      <c r="J96" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="K96" s="3" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="97">
@@ -3286,31 +3628,33 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Nayan Choudhury</t>
+          <t>Pranjal Saikia</t>
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="G97" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="H97" s="3" t="n">
-        <v>79</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr"/>
       <c r="I97" s="3" t="n">
         <v>86</v>
       </c>
+      <c r="J97" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="K97" s="3" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -3319,30 +3663,32 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Pranjal Saikia</t>
+          <t>Himangshu Dutta</t>
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="G98" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="H98" s="3" t="n">
-        <v>92</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr"/>
       <c r="I98" s="3" t="n">
-        <v>86</v>
+        <v>82</v>
+      </c>
+      <c r="J98" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="K98" s="3" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="99">
@@ -3352,30 +3698,32 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Himangshu Dutta</t>
+          <t>Himangshu Bora</t>
         </is>
       </c>
       <c r="D99" s="3" t="n">
         <v>39</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="G99" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="H99" s="3" t="n">
-        <v>67</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="3" t="n">
-        <v>82</v>
+        <v>61</v>
+      </c>
+      <c r="J99" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="K99" s="3" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="100">
@@ -3385,30 +3733,32 @@
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Himangshu Bora</t>
+          <t>Gitika Choudhury</t>
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="E100" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="J100" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="F100" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="G100" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="H100" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="I100" s="3" t="n">
-        <v>61</v>
+      <c r="K100" s="3" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="101">
@@ -3418,63 +3768,67 @@
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Gitika Choudhury</t>
+          <t>Gitika Sharma</t>
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="G101" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="H101" s="3" t="n">
-        <v>37</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr"/>
       <c r="I101" s="3" t="n">
-        <v>42</v>
+        <v>74</v>
+      </c>
+      <c r="J101" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="K101" s="3" t="n">
+        <v>91</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Class 7</t>
+          <t>Class 8</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Gitika Sharma</t>
+          <t>Abhijit Baruah</t>
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="G102" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="H102" s="3" t="n">
-        <v>91</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr"/>
       <c r="I102" s="3" t="n">
-        <v>74</v>
+        <v>50</v>
+      </c>
+      <c r="J102" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="K102" s="3" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="103">
@@ -3484,31 +3838,33 @@
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Abhijit Baruah</t>
+          <t>Kaushik Choudhury</t>
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="G103" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="H103" s="3" t="n">
-        <v>40</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr"/>
       <c r="I103" s="3" t="n">
         <v>50</v>
       </c>
+      <c r="J103" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="K103" s="3" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -3517,30 +3873,32 @@
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Kaushik Choudhury</t>
+          <t>Dimpi Medhi</t>
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="G104" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="H104" s="3" t="n">
         <v>74</v>
       </c>
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr"/>
       <c r="I104" s="3" t="n">
-        <v>50</v>
+        <v>20</v>
+      </c>
+      <c r="J104" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="K104" s="3" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="105">
@@ -3550,30 +3908,32 @@
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Dimpi Medhi</t>
+          <t>Pranjal Dutta</t>
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>74</v>
-      </c>
-      <c r="G105" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="H105" s="3" t="n">
-        <v>67</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr"/>
       <c r="I105" s="3" t="n">
-        <v>20</v>
+        <v>73</v>
+      </c>
+      <c r="J105" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="K105" s="3" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="106">
@@ -3583,30 +3943,32 @@
         </is>
       </c>
       <c r="B106" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Pranjal Dutta</t>
+          <t>Mintu Bora</t>
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="G106" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="H106" s="3" t="n">
-        <v>50</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr"/>
       <c r="I106" s="3" t="n">
-        <v>73</v>
+        <v>42</v>
+      </c>
+      <c r="J106" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="K106" s="3" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="107">
@@ -3616,30 +3978,32 @@
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Mintu Bora</t>
+          <t>Partha Sarmah</t>
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>74</v>
-      </c>
-      <c r="G107" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="H107" s="3" t="n">
-        <v>61</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr"/>
       <c r="I107" s="3" t="n">
-        <v>42</v>
+        <v>97</v>
+      </c>
+      <c r="J107" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="K107" s="3" t="n">
+        <v>77</v>
       </c>
     </row>
     <row r="108">
@@ -3649,30 +4013,32 @@
         </is>
       </c>
       <c r="B108" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Partha Sarmah</t>
+          <t>Pallabi Nath</t>
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="G108" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="H108" s="3" t="n">
-        <v>77</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr"/>
       <c r="I108" s="3" t="n">
-        <v>97</v>
+        <v>56</v>
+      </c>
+      <c r="J108" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="K108" s="3" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="109">
@@ -3682,30 +4048,32 @@
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Pallabi Nath</t>
+          <t>Partha Choudhury</t>
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="F109" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="G109" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="H109" s="3" t="n">
-        <v>36</v>
-      </c>
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr"/>
       <c r="I109" s="3" t="n">
-        <v>56</v>
+        <v>92</v>
+      </c>
+      <c r="J109" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="K109" s="3" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="110">
@@ -3715,30 +4083,32 @@
         </is>
       </c>
       <c r="B110" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Partha Choudhury</t>
+          <t>Partha Baruah</t>
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="G110" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="H110" s="3" t="n">
-        <v>84</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr"/>
       <c r="I110" s="3" t="n">
-        <v>92</v>
+        <v>91</v>
+      </c>
+      <c r="J110" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="K110" s="3" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="111">
@@ -3748,63 +4118,67 @@
         </is>
       </c>
       <c r="B111" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Partha Baruah</t>
+          <t>Hirak Hazarika</t>
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="G111" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="H111" s="3" t="n">
-        <v>34</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr"/>
       <c r="I111" s="3" t="n">
-        <v>91</v>
+        <v>80</v>
+      </c>
+      <c r="J111" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="K111" s="3" t="n">
+        <v>97</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Class 8</t>
+          <t>Class 9</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Hirak Hazarika</t>
+          <t>Kasturi Dutta</t>
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="G112" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="H112" s="3" t="n">
-        <v>97</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr"/>
       <c r="I112" s="3" t="n">
-        <v>80</v>
+        <v>78</v>
+      </c>
+      <c r="J112" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="K112" s="3" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="113">
@@ -3814,30 +4188,32 @@
         </is>
       </c>
       <c r="B113" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Kasturi Dutta</t>
+          <t>Rahul Rabha</t>
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="G113" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="H113" s="3" t="n">
-        <v>84</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr"/>
       <c r="I113" s="3" t="n">
-        <v>78</v>
+        <v>36</v>
+      </c>
+      <c r="J113" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="K113" s="3" t="n">
+        <v>83</v>
       </c>
     </row>
     <row r="114">
@@ -3847,30 +4223,32 @@
         </is>
       </c>
       <c r="B114" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Rahul Rabha</t>
+          <t>Utpal Bora</t>
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="G114" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr"/>
+      <c r="I114" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="J114" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="K114" s="3" t="n">
         <v>66</v>
-      </c>
-      <c r="H114" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="I114" s="3" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="115">
@@ -3880,30 +4258,32 @@
         </is>
       </c>
       <c r="B115" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Utpal Bora</t>
+          <t>Dipankar Medhi</t>
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="G115" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="H115" s="3" t="n">
-        <v>66</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr"/>
       <c r="I115" s="3" t="n">
-        <v>76</v>
+        <v>56</v>
+      </c>
+      <c r="J115" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="K115" s="3" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="116">
@@ -3913,30 +4293,32 @@
         </is>
       </c>
       <c r="B116" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Dipankar Medhi</t>
+          <t>Rima Saikia</t>
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="G116" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="H116" s="3" t="n">
-        <v>39</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr"/>
       <c r="I116" s="3" t="n">
-        <v>56</v>
+        <v>41</v>
+      </c>
+      <c r="J116" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="K116" s="3" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="117">
@@ -3946,30 +4328,32 @@
         </is>
       </c>
       <c r="B117" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Rima Saikia</t>
+          <t>Abhijit Sharma</t>
         </is>
       </c>
       <c r="D117" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr"/>
+      <c r="I117" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="E117" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="F117" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="G117" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="H117" s="3" t="n">
-        <v>78</v>
-      </c>
-      <c r="I117" s="3" t="n">
-        <v>41</v>
+      <c r="J117" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="K117" s="3" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="118">
@@ -3979,30 +4363,32 @@
         </is>
       </c>
       <c r="B118" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Abhijit Sharma</t>
+          <t>Rimjim Das</t>
         </is>
       </c>
       <c r="D118" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr"/>
+      <c r="I118" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="J118" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="E118" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="F118" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="G118" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="H118" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="I118" s="3" t="n">
-        <v>72</v>
+      <c r="K118" s="3" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="119">
@@ -4012,30 +4398,32 @@
         </is>
       </c>
       <c r="B119" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Rimjim Das</t>
+          <t>Partha Nath</t>
         </is>
       </c>
       <c r="D119" s="3" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="G119" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr"/>
+      <c r="I119" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="H119" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="I119" s="3" t="n">
-        <v>43</v>
+      <c r="J119" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="K119" s="3" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="120">
@@ -4045,30 +4433,32 @@
         </is>
       </c>
       <c r="B120" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Partha Nath</t>
+          <t>Manash Rabha</t>
         </is>
       </c>
       <c r="D120" s="3" t="n">
         <v>66</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="G120" s="3" t="n">
-        <v>86</v>
-      </c>
-      <c r="H120" s="3" t="n">
-        <v>96</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr"/>
       <c r="I120" s="3" t="n">
-        <v>34</v>
+        <v>55</v>
+      </c>
+      <c r="J120" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="K120" s="3" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="121">
@@ -4078,63 +4468,67 @@
         </is>
       </c>
       <c r="B121" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Manash Rabha</t>
+          <t>Mitali Kalita</t>
         </is>
       </c>
       <c r="D121" s="3" t="n">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="G121" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="H121" s="3" t="n">
-        <v>56</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr"/>
       <c r="I121" s="3" t="n">
-        <v>55</v>
+        <v>88</v>
+      </c>
+      <c r="J121" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="K121" s="3" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Class 9</t>
+          <t>Class 10</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Mitali Kalita</t>
+          <t>Pooja Choudhury</t>
         </is>
       </c>
       <c r="D122" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr"/>
+      <c r="I122" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="J122" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="E122" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="F122" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="G122" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="H122" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="I122" s="3" t="n">
-        <v>88</v>
+      <c r="K122" s="3" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="123">
@@ -4144,30 +4538,32 @@
         </is>
       </c>
       <c r="B123" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Pooja Choudhury</t>
+          <t>Kangkan Mahanta</t>
         </is>
       </c>
       <c r="D123" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="F123" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="E123" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="F123" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="G123" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="H123" s="3" t="n">
-        <v>65</v>
-      </c>
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr"/>
       <c r="I123" s="3" t="n">
-        <v>40</v>
+        <v>76</v>
+      </c>
+      <c r="J123" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="K123" s="3" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="124">
@@ -4177,30 +4573,32 @@
         </is>
       </c>
       <c r="B124" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Kangkan Mahanta</t>
+          <t>Jyotirmoy Sarmah</t>
         </is>
       </c>
       <c r="D124" s="3" t="n">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="G124" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="H124" s="3" t="n">
-        <v>48</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr"/>
       <c r="I124" s="3" t="n">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="J124" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="K124" s="3" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="125">
@@ -4210,30 +4608,32 @@
         </is>
       </c>
       <c r="B125" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Jyotirmoy Sarmah</t>
+          <t>Juri Rabha</t>
         </is>
       </c>
       <c r="D125" s="3" t="n">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="G125" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="H125" s="3" t="n">
-        <v>90</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr"/>
       <c r="I125" s="3" t="n">
-        <v>70</v>
+        <v>58</v>
+      </c>
+      <c r="J125" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="K125" s="3" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="126">
@@ -4243,30 +4643,32 @@
         </is>
       </c>
       <c r="B126" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Juri Rabha</t>
+          <t>Mamoni Bhattacharya</t>
         </is>
       </c>
       <c r="D126" s="3" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="G126" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="H126" s="3" t="n">
-        <v>40</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr"/>
       <c r="I126" s="3" t="n">
-        <v>58</v>
+        <v>75</v>
+      </c>
+      <c r="J126" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="K126" s="3" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="127">
@@ -4276,30 +4678,32 @@
         </is>
       </c>
       <c r="B127" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Mamoni Bhattacharya</t>
+          <t>Aarav Saikia</t>
         </is>
       </c>
       <c r="D127" s="3" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E127" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="F127" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr"/>
+      <c r="I127" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="J127" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="K127" s="3" t="n">
         <v>54</v>
-      </c>
-      <c r="F127" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="G127" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="H127" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="I127" s="3" t="n">
-        <v>75</v>
       </c>
     </row>
     <row r="128">
@@ -4309,30 +4713,32 @@
         </is>
       </c>
       <c r="B128" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Aarav Saikia</t>
+          <t>Mitali Dutta</t>
         </is>
       </c>
       <c r="D128" s="3" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>78</v>
-      </c>
-      <c r="G128" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="H128" s="3" t="n">
-        <v>54</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr"/>
       <c r="I128" s="3" t="n">
-        <v>40</v>
+        <v>72</v>
+      </c>
+      <c r="J128" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="K128" s="3" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="129">
@@ -4342,30 +4748,32 @@
         </is>
       </c>
       <c r="B129" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Mitali Dutta</t>
+          <t>Manash Gogoi</t>
         </is>
       </c>
       <c r="D129" s="3" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>67</v>
-      </c>
-      <c r="G129" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="H129" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr"/>
+      <c r="I129" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="I129" s="3" t="n">
-        <v>72</v>
+      <c r="J129" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="K129" s="3" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="130">
@@ -4375,30 +4783,32 @@
         </is>
       </c>
       <c r="B130" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Manash Gogoi</t>
+          <t>Partha Dutta</t>
         </is>
       </c>
       <c r="D130" s="3" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="G130" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="H130" s="3" t="n">
-        <v>60</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr"/>
       <c r="I130" s="3" t="n">
-        <v>58</v>
+        <v>63</v>
+      </c>
+      <c r="J130" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="K130" s="3" t="n">
+        <v>92</v>
       </c>
     </row>
     <row r="131">
@@ -4408,63 +4818,32 @@
         </is>
       </c>
       <c r="B131" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Partha Dutta</t>
+          <t>Aarav Das</t>
         </is>
       </c>
       <c r="D131" s="3" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="G131" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="H131" s="3" t="n">
-        <v>92</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr"/>
       <c r="I131" s="3" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>Class 10</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>Aarav Das</t>
-        </is>
-      </c>
-      <c r="D132" s="3" t="n">
-        <v>69</v>
-      </c>
-      <c r="E132" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="F132" s="3" t="n">
-        <v>69</v>
-      </c>
-      <c r="G132" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="J131" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="H132" s="3" t="n">
+      <c r="K131" s="3" t="n">
         <v>86</v>
-      </c>
-      <c r="I132" s="3" t="n">
-        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/results/onxxgawftv.xlsx
+++ b/results/onxxgawftv.xlsx
@@ -443,20 +443,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K131"/>
+  <dimension ref="A1:N131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -515,6 +518,21 @@
           <t>Social Science</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Elective: Hindi</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Elective: Sanskrit</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Elective: Adv. Mathematics</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -527,25 +545,28 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Rituparna Nath</t>
+          <t>Hirak Deka</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -558,25 +579,28 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Kaushik Boro</t>
+          <t>Mamoni Deka</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -589,25 +613,28 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Pallabi Bora</t>
+          <t>Dipankar Saikia</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -620,25 +647,28 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Chayan Deka</t>
+          <t>Hirak Nath</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -651,25 +681,28 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Sourav Sarmah</t>
+          <t>Himangshu Kalita</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -682,25 +715,28 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Barnali Hazarika</t>
+          <t>Mitali Talukdar</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>97</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -713,25 +749,28 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Sourav Sharma</t>
+          <t>Mamoni Bhattacharya</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>49</v>
+        <v>97</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -744,25 +783,28 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Rima Baruah</t>
+          <t>Nirupama Boro</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -775,25 +817,28 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Bikash Bora</t>
+          <t>Rimjim Das</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -806,25 +851,28 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Kangkan Dutta</t>
+          <t>Rituparna Deka</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -837,25 +885,28 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nirupama Boro</t>
+          <t>Juri Boro</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -868,25 +919,28 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Himangshu Kakati</t>
+          <t>Dimpi Gogoi</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
         <v>48</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -899,25 +953,28 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Aarav Bhattacharya</t>
+          <t>Himangshu Saikia</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -930,25 +987,28 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Chayan Saikia</t>
+          <t>Abhijit Kalita</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -961,25 +1021,28 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Sangita Mahanta</t>
+          <t>Mintu Medhi</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>96</v>
+        <v>42</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -992,25 +1055,28 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Rahul Hazarika</t>
+          <t>Chayan Boro</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1023,25 +1089,28 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Rupam Baruah</t>
+          <t>Rahul Gogoi</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>98</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1054,25 +1123,28 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Dimpi Das</t>
+          <t>Abhijit Saikia</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1085,25 +1157,28 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Chayan Sarmah</t>
+          <t>Aarav Bhattacharya</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1116,25 +1191,28 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Bikash Rabha</t>
+          <t>Bikash Hazarika</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1147,25 +1225,28 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Rituparna Bhattacharya</t>
+          <t>Aarav Das</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1178,25 +1259,28 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Rahul Saikia</t>
+          <t>Dipankar Baruah</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="E23" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="G23" s="3" t="n">
         <v>65</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>52</v>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1209,25 +1293,28 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Sumi Deka</t>
+          <t>Ankita Gogoi</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>37</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1240,25 +1327,28 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Chayan Boro</t>
+          <t>Kangkan Hazarika</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1271,25 +1361,28 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Utpal Rabha</t>
+          <t>Ankita Mahanta</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1302,25 +1395,28 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Anaya Mahanta</t>
+          <t>Juri Dutta</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1333,25 +1429,28 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Karabi Nath</t>
+          <t>Himangshu Choudhury</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1364,25 +1463,28 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Barnali Boro</t>
+          <t>Utpal Nath</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1395,25 +1497,28 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Karabi Deka</t>
+          <t>Pranjal Talukdar</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1426,25 +1531,28 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Kangkan Boro</t>
+          <t>Nayan Kalita</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1457,27 +1565,30 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Dipankar Saikia</t>
+          <t>Ankita Sarmah</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="3" t="n">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1490,27 +1601,30 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Mamoni Choudhury</t>
+          <t>Mamoni Das</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="3" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1523,27 +1637,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Dipankar Baruah</t>
+          <t>Kaushik Mahanta</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="3" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1556,27 +1673,30 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Mitali Nath</t>
+          <t>Pranjal Choudhury</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="3" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1589,27 +1709,30 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Anaya Hazarika</t>
+          <t>Jyotirmoy Hazarika</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="3" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1622,27 +1745,30 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Rahul Kalita</t>
+          <t>Mamoni Choudhury</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="3" t="n">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1655,27 +1781,30 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Kaushik Deka</t>
+          <t>Trishna Talukdar</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>37</v>
+        <v>83</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="3" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1688,27 +1817,30 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Mamoni Sarmah</t>
+          <t>Rupam Dutta</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="3" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1721,27 +1853,30 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Rupam Kakati</t>
+          <t>Hirak Mahanta</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="3" t="n">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1754,27 +1889,30 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Sangita Deka</t>
+          <t>Gitika Nath</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="3" t="n">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1787,27 +1925,30 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Anaya Saikia</t>
+          <t>Rimjim Kakati</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="3" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1820,27 +1961,30 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Pranjal Rabha</t>
+          <t>Karabi Bora</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="3" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1853,27 +1997,30 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Juri Bora</t>
+          <t>Kasturi Bhattacharya</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="3" t="n">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1886,27 +2033,30 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Ankita Sarmah</t>
+          <t>Partha Boro</t>
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="3" t="n">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1919,27 +2069,30 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Jyotirmoy Das</t>
+          <t>Rimjim Bora</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="3" t="n">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1952,27 +2105,30 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Kaushik Gogoi</t>
+          <t>Sumi Saikia</t>
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="3" t="n">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1985,27 +2141,30 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Gitika Bora</t>
+          <t>Pooja Kakati</t>
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="3" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2018,27 +2177,30 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Nayan Medhi</t>
+          <t>Sumi Kalita</t>
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>98</v>
+        <v>44</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="3" t="n">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2051,27 +2213,30 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Pooja Das</t>
+          <t>Barnali Kakati</t>
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="3" t="n">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2084,27 +2249,30 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Rahul Sharma</t>
+          <t>Partha Gogoi</t>
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="3" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2117,27 +2285,30 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Sourav Kalita</t>
+          <t>Mamoni Mahanta</t>
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>82</v>
+        <v>35</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="3" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2150,27 +2321,30 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Nayan Kakati</t>
+          <t>Dimpi Hazarika</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="3" t="n">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2183,27 +2357,30 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Mintu Kakati</t>
+          <t>Priya Dutta</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="3" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2216,27 +2393,30 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Rima Choudhury</t>
+          <t>Ankita Nath</t>
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="3" t="n">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2249,27 +2429,30 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Utpal Medhi</t>
+          <t>Priya Talukdar</t>
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="3" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2282,27 +2465,30 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Partha Boro</t>
+          <t>Partha Rabha</t>
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="3" t="n">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2315,27 +2501,30 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Nirupama Kalita</t>
+          <t>Trishna Boro</t>
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="3" t="n">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2348,27 +2537,30 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Mintu Sharma</t>
+          <t>Pooja Boro</t>
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="3" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2381,27 +2573,30 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Dipankar Choudhury</t>
+          <t>Sourav Gogoi</t>
         </is>
       </c>
       <c r="D60" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F60" s="3" t="n">
         <v>57</v>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="F60" s="3" t="n">
-        <v>98</v>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="3" t="n">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2414,27 +2609,30 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Priya Sarmah</t>
+          <t>Pooja Sarmah</t>
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="3" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2447,27 +2645,30 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Rimjim Kakati</t>
+          <t>Ankita Saikia</t>
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="F62" s="3" t="n">
         <v>89</v>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="3" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2480,27 +2681,30 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Sourav Choudhury</t>
+          <t>Bikash Talukdar</t>
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>97</v>
+        <v>18</v>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="3" t="n">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2513,27 +2717,30 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Karabi Sarmah</t>
+          <t>Mitali Bhattacharya</t>
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="3" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2546,27 +2753,30 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Kaushik Mahanta</t>
+          <t>Dimpi Rabha</t>
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="3" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2579,27 +2789,30 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Nirupama Gogoi</t>
+          <t>Bikash Rabha</t>
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="3" t="n">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2612,27 +2825,30 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Aarav Kakati</t>
+          <t>Pallabi Boro</t>
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="3" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -2645,27 +2861,30 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Rimjim Bora</t>
+          <t>Karabi Baruah</t>
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="3" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2678,27 +2897,30 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Sourav Bora</t>
+          <t>Kasturi Sharma</t>
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="3" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2711,27 +2933,30 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Kaushik Bhattacharya</t>
+          <t>Pooja Bhattacharya</t>
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="3" t="n">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -2744,27 +2969,30 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Sumi Kakati</t>
+          <t>Partha Bora</t>
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>93</v>
+        <v>34</v>
       </c>
       <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="3" t="n">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -2777,27 +3005,30 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Nayan Hazarika</t>
+          <t>Juri Kakati</t>
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="3" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -2810,27 +3041,30 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Himangshu Rabha</t>
+          <t>Dhruba Nath</t>
         </is>
       </c>
       <c r="D73" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E73" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="E73" s="3" t="n">
-        <v>81</v>
-      </c>
       <c r="F73" s="3" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="3" t="n">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -2843,27 +3077,30 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Jyotirmoy Kakati</t>
+          <t>Rupam Bhattacharya</t>
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="3" t="n">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -2876,27 +3113,30 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Barnali Kakati</t>
+          <t>Manash Hazarika</t>
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="3" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2909,27 +3149,30 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Mamoni Rabha</t>
+          <t>Trishna Medhi</t>
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>46</v>
+        <v>94</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="3" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2942,27 +3185,30 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Sumi Gogoi</t>
+          <t>Hirak Choudhury</t>
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="3" t="n">
-        <v>92</v>
+        <v>38</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -2975,27 +3221,30 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Rimjim Hazarika</t>
+          <t>Nirupama Bhattacharya</t>
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="3" t="n">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -3008,27 +3257,30 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Dimpi Mahanta</t>
+          <t>Trishna Sharma</t>
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="3" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -3041,27 +3293,30 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Jyotirmoy Bora</t>
+          <t>Rima Boro</t>
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="3" t="n">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -3074,27 +3329,30 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Juri Boro</t>
+          <t>Utpal Sarmah</t>
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="3" t="n">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -3107,29 +3365,32 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Gitika Baruah</t>
+          <t>Karabi Saikia</t>
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="3" t="n">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="K82" s="3" t="n">
-        <v>35</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -3142,29 +3403,32 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Rituparna Mahanta</t>
+          <t>Himangshu Dutta</t>
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="G83" s="2" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr"/>
       <c r="I83" s="3" t="n">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="K83" s="3" t="n">
-        <v>62</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -3177,29 +3441,32 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Mintu Sarmah</t>
+          <t>Pranjal Rabha</t>
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="3" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>77</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -3212,29 +3479,32 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Bikash Hazarika</t>
+          <t>Rahul Kalita</t>
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="J85" s="3" t="n">
         <v>69</v>
       </c>
-      <c r="J85" s="3" t="n">
-        <v>58</v>
-      </c>
       <c r="K85" s="3" t="n">
-        <v>51</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -3247,29 +3517,32 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Rahul Choudhury</t>
+          <t>Utpal Bora</t>
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>56</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -3282,29 +3555,32 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Sumi Sarmah</t>
+          <t>Sourav Sarmah</t>
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr"/>
       <c r="I87" s="3" t="n">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="K87" s="3" t="n">
-        <v>56</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -3317,29 +3593,32 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Sumi Kalita</t>
+          <t>Dimpi Medhi</t>
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="3" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>36</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -3352,29 +3631,32 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Priya Rabha</t>
+          <t>Manash Mahanta</t>
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr"/>
       <c r="I89" s="3" t="n">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>57</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -3387,29 +3669,32 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Sumi Dutta</t>
+          <t>Utpal Saikia</t>
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr"/>
       <c r="I90" s="3" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="K90" s="3" t="n">
-        <v>71</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -3422,29 +3707,32 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Rupam Gogoi</t>
+          <t>Mamoni Talukdar</t>
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr"/>
       <c r="I91" s="3" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>76</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -3457,29 +3745,32 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Kasturi Rabha</t>
+          <t>Mamoni Medhi</t>
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr"/>
       <c r="I92" s="3" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>90</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -3492,29 +3783,32 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Ankita Saikia</t>
+          <t>Abhijit Choudhury</t>
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr"/>
       <c r="I93" s="3" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="K93" s="3" t="n">
-        <v>78</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -3527,29 +3821,32 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Hirak Kakati</t>
+          <t>Rituparna Hazarika</t>
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="2" t="inlineStr"/>
       <c r="I94" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="J94" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="K94" s="3" t="n">
         <v>95</v>
       </c>
-      <c r="J94" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="K94" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -3562,29 +3859,32 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Chayan Bhattacharya</t>
+          <t>Hirak Medhi</t>
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="G95" s="2" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr"/>
       <c r="I95" s="3" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="K95" s="3" t="n">
-        <v>93</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -3597,29 +3897,32 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Nayan Choudhury</t>
+          <t>Utpal Deka</t>
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="inlineStr"/>
       <c r="I96" s="3" t="n">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="K96" s="3" t="n">
-        <v>79</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -3632,29 +3935,32 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Pranjal Saikia</t>
+          <t>Sumi Dutta</t>
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="G97" s="2" t="inlineStr"/>
       <c r="H97" s="2" t="inlineStr"/>
       <c r="I97" s="3" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J97" s="3" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="K97" s="3" t="n">
-        <v>92</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -3667,29 +3973,32 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Himangshu Dutta</t>
+          <t>Juri Sharma</t>
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr"/>
       <c r="I98" s="3" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="J98" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="K98" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="K98" s="3" t="n">
-        <v>67</v>
-      </c>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -3702,29 +4011,32 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Himangshu Bora</t>
+          <t>Kangkan Dutta</t>
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="3" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>61</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -3737,29 +4049,32 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Gitika Choudhury</t>
+          <t>Sumi Choudhury</t>
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr"/>
       <c r="I100" s="3" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>37</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -3772,29 +4087,32 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Gitika Sharma</t>
+          <t>Kangkan Choudhury</t>
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="G101" s="2" t="inlineStr"/>
       <c r="H101" s="2" t="inlineStr"/>
       <c r="I101" s="3" t="n">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>91</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -3807,29 +4125,32 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Abhijit Baruah</t>
+          <t>Sourav Boro</t>
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr"/>
       <c r="I102" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J102" s="3" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K102" s="3" t="n">
-        <v>40</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -3842,29 +4163,32 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Kaushik Choudhury</t>
+          <t>Utpal Hazarika</t>
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr"/>
       <c r="I103" s="3" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>74</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -3877,29 +4201,32 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Dimpi Medhi</t>
+          <t>Rima Das</t>
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr"/>
       <c r="I104" s="3" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="K104" s="3" t="n">
-        <v>67</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -3912,29 +4239,32 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Pranjal Dutta</t>
+          <t>Jyotirmoy Choudhury</t>
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr"/>
       <c r="I105" s="3" t="n">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="J105" s="3" t="n">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="K105" s="3" t="n">
-        <v>50</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -3947,29 +4277,32 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Mintu Bora</t>
+          <t>Rima Sarmah</t>
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr"/>
       <c r="I106" s="3" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>61</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -3982,29 +4315,32 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Partha Sarmah</t>
+          <t>Sourav Medhi</t>
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="G107" s="2" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr"/>
       <c r="I107" s="3" t="n">
-        <v>97</v>
+        <v>55</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>77</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -4017,29 +4353,32 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Pallabi Nath</t>
+          <t>Gitika Boro</t>
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr"/>
       <c r="I108" s="3" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="K108" s="3" t="n">
-        <v>36</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -4052,29 +4391,32 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Partha Choudhury</t>
+          <t>Pooja Baruah</t>
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr"/>
       <c r="I109" s="3" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="J109" s="3" t="n">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="K109" s="3" t="n">
-        <v>84</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="L109" s="2" t="inlineStr"/>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -4087,29 +4429,32 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Partha Baruah</t>
+          <t>Nayan Bora</t>
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr"/>
       <c r="I110" s="3" t="n">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>34</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -4122,29 +4467,32 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Hirak Hazarika</t>
+          <t>Hirak Saikia</t>
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr"/>
       <c r="I111" s="3" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>97</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="L111" s="2" t="inlineStr"/>
+      <c r="M111" s="2" t="inlineStr"/>
+      <c r="N111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -4157,28 +4505,31 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Kasturi Dutta</t>
+          <t>Pranjal Deka</t>
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="G112" s="2" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr"/>
-      <c r="I112" s="3" t="n">
-        <v>78</v>
-      </c>
+      <c r="I112" s="2" t="inlineStr"/>
       <c r="J112" s="3" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>84</v>
+        <v>25</v>
+      </c>
+      <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="2" t="inlineStr"/>
+      <c r="N112" s="3" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="113">
@@ -4192,29 +4543,32 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Rahul Rabha</t>
+          <t>Karabi Sharma</t>
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="G113" s="2" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr"/>
-      <c r="I113" s="3" t="n">
-        <v>36</v>
-      </c>
+      <c r="I113" s="2" t="inlineStr"/>
       <c r="J113" s="3" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="K113" s="3" t="n">
-        <v>83</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="L113" s="2" t="inlineStr"/>
+      <c r="M113" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="N113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -4227,29 +4581,32 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Utpal Bora</t>
+          <t>Jyotirmoy Dutta</t>
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="E114" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="F114" s="3" t="n">
         <v>83</v>
-      </c>
-      <c r="F114" s="3" t="n">
-        <v>79</v>
       </c>
       <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr"/>
-      <c r="I114" s="3" t="n">
-        <v>76</v>
-      </c>
+      <c r="I114" s="2" t="inlineStr"/>
       <c r="J114" s="3" t="n">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="K114" s="3" t="n">
-        <v>66</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="L114" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr"/>
+      <c r="N114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -4262,29 +4619,32 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Dipankar Medhi</t>
+          <t>Nayan Rabha</t>
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="G115" s="2" t="inlineStr"/>
       <c r="H115" s="2" t="inlineStr"/>
-      <c r="I115" s="3" t="n">
-        <v>56</v>
-      </c>
+      <c r="I115" s="2" t="inlineStr"/>
       <c r="J115" s="3" t="n">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>39</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="L115" s="2" t="inlineStr"/>
+      <c r="M115" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="N115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -4297,29 +4657,32 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Rima Saikia</t>
+          <t>Sumi Kakati</t>
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr"/>
-      <c r="I116" s="3" t="n">
-        <v>41</v>
-      </c>
+      <c r="I116" s="2" t="inlineStr"/>
       <c r="J116" s="3" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>78</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="L116" s="2" t="inlineStr"/>
+      <c r="M116" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="N116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -4332,28 +4695,31 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Abhijit Sharma</t>
+          <t>Jyotirmoy Sarmah</t>
         </is>
       </c>
       <c r="D117" s="3" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr"/>
-      <c r="I117" s="3" t="n">
-        <v>72</v>
-      </c>
+      <c r="I117" s="2" t="inlineStr"/>
       <c r="J117" s="3" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K117" s="3" t="n">
-        <v>66</v>
+        <v>88</v>
+      </c>
+      <c r="L117" s="2" t="inlineStr"/>
+      <c r="M117" s="2" t="inlineStr"/>
+      <c r="N117" s="3" t="n">
+        <v>89</v>
       </c>
     </row>
     <row r="118">
@@ -4367,29 +4733,32 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Rimjim Das</t>
+          <t>Mitali Baruah</t>
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr"/>
-      <c r="I118" s="3" t="n">
-        <v>43</v>
-      </c>
+      <c r="I118" s="2" t="inlineStr"/>
       <c r="J118" s="3" t="n">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>56</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="L118" s="2" t="inlineStr"/>
+      <c r="M118" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="N118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -4402,29 +4771,32 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Partha Nath</t>
+          <t>Nayan Choudhury</t>
         </is>
       </c>
       <c r="D119" s="3" t="n">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr"/>
-      <c r="I119" s="3" t="n">
-        <v>34</v>
-      </c>
+      <c r="I119" s="2" t="inlineStr"/>
       <c r="J119" s="3" t="n">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="K119" s="3" t="n">
-        <v>96</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="L119" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="M119" s="2" t="inlineStr"/>
+      <c r="N119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -4437,29 +4809,32 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Manash Rabha</t>
+          <t>Dipankar Das</t>
         </is>
       </c>
       <c r="D120" s="3" t="n">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr"/>
-      <c r="I120" s="3" t="n">
-        <v>55</v>
-      </c>
+      <c r="I120" s="2" t="inlineStr"/>
       <c r="J120" s="3" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="K120" s="3" t="n">
-        <v>56</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="N120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -4472,29 +4847,32 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Mitali Kalita</t>
+          <t>Rupam Kakati</t>
         </is>
       </c>
       <c r="D121" s="3" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G121" s="2" t="inlineStr"/>
       <c r="H121" s="2" t="inlineStr"/>
-      <c r="I121" s="3" t="n">
-        <v>88</v>
-      </c>
+      <c r="I121" s="2" t="inlineStr"/>
       <c r="J121" s="3" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>53</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="L121" s="2" t="inlineStr"/>
+      <c r="M121" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="N121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -4507,29 +4885,32 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Pooja Choudhury</t>
+          <t>Dimpi Das</t>
         </is>
       </c>
       <c r="D122" s="3" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G122" s="2" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr"/>
-      <c r="I122" s="3" t="n">
-        <v>40</v>
-      </c>
+      <c r="I122" s="2" t="inlineStr"/>
       <c r="J122" s="3" t="n">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="K122" s="3" t="n">
-        <v>65</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="N122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -4542,29 +4923,32 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Kangkan Mahanta</t>
+          <t>Himangshu Talukdar</t>
         </is>
       </c>
       <c r="D123" s="3" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="G123" s="2" t="inlineStr"/>
       <c r="H123" s="2" t="inlineStr"/>
-      <c r="I123" s="3" t="n">
-        <v>76</v>
-      </c>
+      <c r="I123" s="2" t="inlineStr"/>
       <c r="J123" s="3" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="K123" s="3" t="n">
-        <v>48</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="L123" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="M123" s="2" t="inlineStr"/>
+      <c r="N123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -4577,28 +4961,31 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Jyotirmoy Sarmah</t>
+          <t>Jyotirmoy Nath</t>
         </is>
       </c>
       <c r="D124" s="3" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G124" s="2" t="inlineStr"/>
       <c r="H124" s="2" t="inlineStr"/>
-      <c r="I124" s="3" t="n">
-        <v>70</v>
-      </c>
+      <c r="I124" s="2" t="inlineStr"/>
       <c r="J124" s="3" t="n">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>90</v>
+        <v>86</v>
+      </c>
+      <c r="L124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr"/>
+      <c r="N124" s="3" t="n">
+        <v>87</v>
       </c>
     </row>
     <row r="125">
@@ -4612,29 +4999,32 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Juri Rabha</t>
+          <t>Barnali Rabha</t>
         </is>
       </c>
       <c r="D125" s="3" t="n">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>92</v>
+        <v>24</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G125" s="2" t="inlineStr"/>
       <c r="H125" s="2" t="inlineStr"/>
-      <c r="I125" s="3" t="n">
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="J125" s="3" t="n">
-        <v>85</v>
-      </c>
       <c r="K125" s="3" t="n">
-        <v>40</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="L125" s="2" t="inlineStr"/>
+      <c r="M125" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="N125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -4647,29 +5037,32 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Mamoni Bhattacharya</t>
+          <t>Mitali Deka</t>
         </is>
       </c>
       <c r="D126" s="3" t="n">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr"/>
-      <c r="I126" s="3" t="n">
-        <v>75</v>
-      </c>
+      <c r="I126" s="2" t="inlineStr"/>
       <c r="J126" s="3" t="n">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="K126" s="3" t="n">
-        <v>66</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="L126" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="M126" s="2" t="inlineStr"/>
+      <c r="N126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -4682,28 +5075,31 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Aarav Saikia</t>
+          <t>Mitali Medhi</t>
         </is>
       </c>
       <c r="D127" s="3" t="n">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="G127" s="2" t="inlineStr"/>
       <c r="H127" s="2" t="inlineStr"/>
-      <c r="I127" s="3" t="n">
-        <v>40</v>
-      </c>
+      <c r="I127" s="2" t="inlineStr"/>
       <c r="J127" s="3" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="K127" s="3" t="n">
-        <v>54</v>
+        <v>19</v>
+      </c>
+      <c r="L127" s="2" t="inlineStr"/>
+      <c r="M127" s="2" t="inlineStr"/>
+      <c r="N127" s="3" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="128">
@@ -4717,28 +5113,31 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Mitali Dutta</t>
+          <t>Juri Deka</t>
         </is>
       </c>
       <c r="D128" s="3" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr"/>
-      <c r="I128" s="3" t="n">
-        <v>72</v>
-      </c>
+      <c r="I128" s="2" t="inlineStr"/>
       <c r="J128" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="K128" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="L128" s="2" t="inlineStr"/>
+      <c r="M128" s="2" t="inlineStr"/>
+      <c r="N128" s="3" t="n">
         <v>51</v>
-      </c>
-      <c r="K128" s="3" t="n">
-        <v>58</v>
       </c>
     </row>
     <row r="129">
@@ -4752,29 +5151,32 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Manash Gogoi</t>
+          <t>Utpal Das</t>
         </is>
       </c>
       <c r="D129" s="3" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="G129" s="2" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr"/>
-      <c r="I129" s="3" t="n">
-        <v>58</v>
-      </c>
+      <c r="I129" s="2" t="inlineStr"/>
       <c r="J129" s="3" t="n">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="K129" s="3" t="n">
-        <v>60</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="L129" s="2" t="inlineStr"/>
+      <c r="M129" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="N129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -4787,28 +5189,31 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Partha Dutta</t>
+          <t>Mitali Sharma</t>
         </is>
       </c>
       <c r="D130" s="3" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr"/>
-      <c r="I130" s="3" t="n">
-        <v>63</v>
-      </c>
+      <c r="I130" s="2" t="inlineStr"/>
       <c r="J130" s="3" t="n">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="K130" s="3" t="n">
-        <v>92</v>
+        <v>91</v>
+      </c>
+      <c r="L130" s="2" t="inlineStr"/>
+      <c r="M130" s="2" t="inlineStr"/>
+      <c r="N130" s="3" t="n">
+        <v>83</v>
       </c>
     </row>
     <row r="131">
@@ -4822,29 +5227,32 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Aarav Das</t>
+          <t>Juri Saikia</t>
         </is>
       </c>
       <c r="D131" s="3" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="G131" s="2" t="inlineStr"/>
       <c r="H131" s="2" t="inlineStr"/>
-      <c r="I131" s="3" t="n">
-        <v>57</v>
-      </c>
+      <c r="I131" s="2" t="inlineStr"/>
       <c r="J131" s="3" t="n">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="K131" s="3" t="n">
-        <v>86</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="L131" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="M131" s="2" t="inlineStr"/>
+      <c r="N131" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/onxxgawftv.xlsx
+++ b/results/onxxgawftv.xlsx
@@ -2289,20 +2289,20 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="3" t="n">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
@@ -2321,24 +2321,24 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Dimpi Hazarika</t>
+          <t>Dimpi Mahanta</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="3" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
@@ -2364,17 +2364,17 @@
         <v>53</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="3" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
@@ -2393,24 +2393,24 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Ankita Nath</t>
+          <t>Karabi Kakati</t>
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="3" t="n">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
@@ -2429,24 +2429,24 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Priya Talukdar</t>
+          <t>Jyotirmoy Nath</t>
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="3" t="n">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
@@ -2465,24 +2465,24 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Partha Rabha</t>
+          <t>Sangita Sharma</t>
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="3" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
@@ -2501,24 +2501,24 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Trishna Boro</t>
+          <t>Gitika Baruah</t>
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="3" t="n">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
@@ -2537,24 +2537,24 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Pooja Boro</t>
+          <t>Ankita Nath</t>
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="3" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
@@ -2573,24 +2573,24 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Sourav Gogoi</t>
+          <t>Rituparna Mahanta</t>
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="3" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
@@ -2609,24 +2609,24 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Pooja Sarmah</t>
+          <t>Priya Mahanta</t>
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="3" t="n">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
@@ -2645,24 +2645,24 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Ankita Saikia</t>
+          <t>Pooja Hazarika</t>
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="3" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
@@ -2681,24 +2681,24 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Bikash Talukdar</t>
+          <t>Ankita Boro</t>
         </is>
       </c>
       <c r="D63" s="3" t="n">
         <v>48</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="3" t="n">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
@@ -2717,24 +2717,24 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Mitali Bhattacharya</t>
+          <t>Partha Rabha</t>
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="3" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
@@ -2753,24 +2753,24 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Dimpi Rabha</t>
+          <t>Barnali Hazarika</t>
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>92</v>
+        <v>24</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="3" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
@@ -2789,24 +2789,24 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Bikash Rabha</t>
+          <t>Rimjim Sarmah</t>
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="3" t="n">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
@@ -2825,24 +2825,24 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Pallabi Boro</t>
+          <t>Sourav Gogoi</t>
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="3" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
@@ -2861,24 +2861,24 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Karabi Baruah</t>
+          <t>Anaya Kakati</t>
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="3" t="n">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
@@ -2897,24 +2897,24 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Kasturi Sharma</t>
+          <t>Manash Medhi</t>
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="3" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
@@ -2933,24 +2933,24 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Pooja Bhattacharya</t>
+          <t>Pranjal Baruah</t>
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="3" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
@@ -2969,24 +2969,24 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Partha Bora</t>
+          <t>Dipankar Sarmah</t>
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="3" t="n">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>27</v>
+        <v>94</v>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
@@ -3005,24 +3005,24 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Juri Kakati</t>
+          <t>Rupam Gogoi</t>
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="3" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
@@ -3041,24 +3041,24 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Dhruba Nath</t>
+          <t>Anaya Kalita</t>
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="3" t="n">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
@@ -3077,24 +3077,24 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Rupam Bhattacharya</t>
+          <t>Rituparna Saikia</t>
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="3" t="n">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
@@ -3113,24 +3113,24 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Manash Hazarika</t>
+          <t>Mitali Hazarika</t>
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E75" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="F75" s="3" t="n">
         <v>80</v>
-      </c>
-      <c r="F75" s="3" t="n">
-        <v>96</v>
       </c>
       <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="3" t="n">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
@@ -3149,24 +3149,24 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Trishna Medhi</t>
+          <t>Chayan Dutta</t>
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F76" s="3" t="n">
         <v>85</v>
       </c>
       <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="3" t="n">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
@@ -3185,24 +3185,24 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Hirak Choudhury</t>
+          <t>Dimpi Saikia</t>
         </is>
       </c>
       <c r="D77" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="F77" s="3" t="n">
         <v>79</v>
-      </c>
-      <c r="E77" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F77" s="3" t="n">
-        <v>66</v>
       </c>
       <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="3" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
@@ -3221,24 +3221,24 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Nirupama Bhattacharya</t>
+          <t>Mamoni Saikia</t>
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="3" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
@@ -3257,24 +3257,24 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Trishna Sharma</t>
+          <t>Nirupama Medhi</t>
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="3" t="n">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
@@ -3293,24 +3293,24 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Rima Boro</t>
+          <t>Aarav Sarmah</t>
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="E80" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="F80" s="3" t="n">
         <v>52</v>
-      </c>
-      <c r="F80" s="3" t="n">
-        <v>34</v>
       </c>
       <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="3" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
@@ -3329,21 +3329,21 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Utpal Sarmah</t>
+          <t>Himangshu Dutta</t>
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="3" t="n">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="I81" s="3" t="n">
         <v>66</v>
@@ -3365,28 +3365,28 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Karabi Saikia</t>
+          <t>Anaya Rabha</t>
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="3" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K82" s="3" t="n">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="L82" s="2" t="inlineStr"/>
       <c r="M82" s="2" t="inlineStr"/>
@@ -3403,28 +3403,28 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Himangshu Dutta</t>
+          <t>Jyotirmoy Kalita</t>
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="E83" s="3" t="n">
         <v>85</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="G83" s="2" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr"/>
       <c r="I83" s="3" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J83" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="K83" s="3" t="n">
         <v>89</v>
-      </c>
-      <c r="K83" s="3" t="n">
-        <v>67</v>
       </c>
       <c r="L83" s="2" t="inlineStr"/>
       <c r="M83" s="2" t="inlineStr"/>
@@ -3441,28 +3441,28 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Pranjal Rabha</t>
+          <t>Abhijit Choudhury</t>
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>19</v>
+        <v>93</v>
       </c>
       <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="3" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="L84" s="2" t="inlineStr"/>
       <c r="M84" s="2" t="inlineStr"/>
@@ -3479,28 +3479,28 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Rahul Kalita</t>
+          <t>Pallabi Dutta</t>
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="3" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="L85" s="2" t="inlineStr"/>
       <c r="M85" s="2" t="inlineStr"/>
@@ -3517,28 +3517,28 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Utpal Bora</t>
+          <t>Chayan Sarmah</t>
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="3" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="L86" s="2" t="inlineStr"/>
       <c r="M86" s="2" t="inlineStr"/>
@@ -3555,28 +3555,28 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Sourav Sarmah</t>
+          <t>Rima Medhi</t>
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr"/>
       <c r="I87" s="3" t="n">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K87" s="3" t="n">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="L87" s="2" t="inlineStr"/>
       <c r="M87" s="2" t="inlineStr"/>
@@ -3593,17 +3593,17 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Dimpi Medhi</t>
+          <t>Pallabi Bhattacharya</t>
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr"/>
@@ -3611,10 +3611,10 @@
         <v>74</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L88" s="2" t="inlineStr"/>
       <c r="M88" s="2" t="inlineStr"/>
@@ -3631,28 +3631,28 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Manash Mahanta</t>
+          <t>Rupam Choudhury</t>
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr"/>
       <c r="I89" s="3" t="n">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="L89" s="2" t="inlineStr"/>
       <c r="M89" s="2" t="inlineStr"/>
@@ -3669,28 +3669,28 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Utpal Saikia</t>
+          <t>Abhijit Bora</t>
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr"/>
       <c r="I90" s="3" t="n">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="K90" s="3" t="n">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="L90" s="2" t="inlineStr"/>
       <c r="M90" s="2" t="inlineStr"/>
@@ -3707,28 +3707,28 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Mamoni Talukdar</t>
+          <t>Barnali Deka</t>
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr"/>
       <c r="I91" s="3" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr"/>
@@ -3745,28 +3745,28 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Mamoni Medhi</t>
+          <t>Sumi Boro</t>
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr"/>
       <c r="I92" s="3" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr"/>
@@ -3783,17 +3783,17 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Abhijit Choudhury</t>
+          <t>Rahul Medhi</t>
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr"/>
@@ -3801,10 +3801,10 @@
         <v>52</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="K93" s="3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr"/>
@@ -3821,28 +3821,28 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Rituparna Hazarika</t>
+          <t>Priya Hazarika</t>
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="2" t="inlineStr"/>
       <c r="I94" s="3" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="J94" s="3" t="n">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="K94" s="3" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr"/>
@@ -3859,28 +3859,28 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Hirak Medhi</t>
+          <t>Rima Gogoi</t>
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="G95" s="2" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr"/>
       <c r="I95" s="3" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="K95" s="3" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr"/>
@@ -3897,28 +3897,28 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Utpal Deka</t>
+          <t>Himangshu Hazarika</t>
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="inlineStr"/>
       <c r="I96" s="3" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="K96" s="3" t="n">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr"/>
@@ -3935,28 +3935,28 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Sumi Dutta</t>
+          <t>Mintu Bora</t>
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="G97" s="2" t="inlineStr"/>
       <c r="H97" s="2" t="inlineStr"/>
       <c r="I97" s="3" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="J97" s="3" t="n">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="K97" s="3" t="n">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="L97" s="2" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr"/>
@@ -3973,28 +3973,28 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Juri Sharma</t>
+          <t>Utpal Mahanta</t>
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr"/>
       <c r="I98" s="3" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="K98" s="3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L98" s="2" t="inlineStr"/>
       <c r="M98" s="2" t="inlineStr"/>
@@ -4011,28 +4011,28 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Kangkan Dutta</t>
+          <t>Pranjal Das</t>
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="3" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="L99" s="2" t="inlineStr"/>
       <c r="M99" s="2" t="inlineStr"/>
@@ -4049,28 +4049,28 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Sumi Choudhury</t>
+          <t>Dipankar Boro</t>
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr"/>
       <c r="I100" s="3" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="L100" s="2" t="inlineStr"/>
       <c r="M100" s="2" t="inlineStr"/>
@@ -4087,28 +4087,28 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Kangkan Choudhury</t>
+          <t>Rima Bora</t>
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G101" s="2" t="inlineStr"/>
       <c r="H101" s="2" t="inlineStr"/>
       <c r="I101" s="3" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="L101" s="2" t="inlineStr"/>
       <c r="M101" s="2" t="inlineStr"/>
@@ -4125,28 +4125,28 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Sourav Boro</t>
+          <t>Manash Hazarika</t>
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr"/>
       <c r="I102" s="3" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="J102" s="3" t="n">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="K102" s="3" t="n">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="L102" s="2" t="inlineStr"/>
       <c r="M102" s="2" t="inlineStr"/>
@@ -4163,28 +4163,28 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Utpal Hazarika</t>
+          <t>Trishna Medhi</t>
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr"/>
       <c r="I103" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="J103" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="J103" s="3" t="n">
-        <v>35</v>
-      </c>
       <c r="K103" s="3" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="L103" s="2" t="inlineStr"/>
       <c r="M103" s="2" t="inlineStr"/>
@@ -4201,28 +4201,28 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Rima Das</t>
+          <t>Rupam Medhi</t>
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr"/>
       <c r="I104" s="3" t="n">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="K104" s="3" t="n">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="L104" s="2" t="inlineStr"/>
       <c r="M104" s="2" t="inlineStr"/>
@@ -4239,28 +4239,28 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Jyotirmoy Choudhury</t>
+          <t>Rituparna Dutta</t>
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr"/>
       <c r="I105" s="3" t="n">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="J105" s="3" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K105" s="3" t="n">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="L105" s="2" t="inlineStr"/>
       <c r="M105" s="2" t="inlineStr"/>
@@ -4277,28 +4277,28 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Rima Sarmah</t>
+          <t>Utpal Bora</t>
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr"/>
       <c r="I106" s="3" t="n">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="L106" s="2" t="inlineStr"/>
       <c r="M106" s="2" t="inlineStr"/>
@@ -4315,28 +4315,28 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Sourav Medhi</t>
+          <t>Nirupama Bhattacharya</t>
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G107" s="2" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr"/>
       <c r="I107" s="3" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="L107" s="2" t="inlineStr"/>
       <c r="M107" s="2" t="inlineStr"/>
@@ -4353,28 +4353,28 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Gitika Boro</t>
+          <t>Abhijit Deka</t>
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr"/>
       <c r="I108" s="3" t="n">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K108" s="3" t="n">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="L108" s="2" t="inlineStr"/>
       <c r="M108" s="2" t="inlineStr"/>
@@ -4391,28 +4391,28 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Pooja Baruah</t>
+          <t>Rima Saikia</t>
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr"/>
       <c r="I109" s="3" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="J109" s="3" t="n">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K109" s="3" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="L109" s="2" t="inlineStr"/>
       <c r="M109" s="2" t="inlineStr"/>
@@ -4429,28 +4429,28 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Nayan Bora</t>
+          <t>Sangita Das</t>
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr"/>
       <c r="I110" s="3" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="L110" s="2" t="inlineStr"/>
       <c r="M110" s="2" t="inlineStr"/>
@@ -4467,28 +4467,28 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Hirak Saikia</t>
+          <t>Abhijit Sharma</t>
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr"/>
       <c r="I111" s="3" t="n">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="L111" s="2" t="inlineStr"/>
       <c r="M111" s="2" t="inlineStr"/>
@@ -4505,31 +4505,31 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Pranjal Deka</t>
+          <t>Rimjim Deka</t>
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="G112" s="2" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr"/>
       <c r="I112" s="2" t="inlineStr"/>
       <c r="J112" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="K112" s="3" t="n">
         <v>40</v>
-      </c>
-      <c r="K112" s="3" t="n">
-        <v>25</v>
       </c>
       <c r="L112" s="2" t="inlineStr"/>
       <c r="M112" s="2" t="inlineStr"/>
       <c r="N112" s="3" t="n">
-        <v>66</v>
+        <v>98</v>
       </c>
     </row>
     <row r="113">
@@ -4543,30 +4543,30 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Karabi Sharma</t>
+          <t>Utpal Sarmah</t>
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G113" s="2" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr"/>
       <c r="I113" s="2" t="inlineStr"/>
       <c r="J113" s="3" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="K113" s="3" t="n">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="L113" s="2" t="inlineStr"/>
       <c r="M113" s="3" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="N113" s="2" t="inlineStr"/>
     </row>
@@ -4581,29 +4581,29 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Jyotirmoy Dutta</t>
+          <t>Manash Talukdar</t>
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr"/>
       <c r="I114" s="2" t="inlineStr"/>
       <c r="J114" s="3" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="K114" s="3" t="n">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="L114" s="3" t="n">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="M114" s="2" t="inlineStr"/>
       <c r="N114" s="2" t="inlineStr"/>
@@ -4619,30 +4619,30 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Nayan Rabha</t>
+          <t>Trishna Kakati</t>
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="G115" s="2" t="inlineStr"/>
       <c r="H115" s="2" t="inlineStr"/>
       <c r="I115" s="2" t="inlineStr"/>
       <c r="J115" s="3" t="n">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="L115" s="2" t="inlineStr"/>
       <c r="M115" s="3" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="N115" s="2" t="inlineStr"/>
     </row>
@@ -4657,31 +4657,31 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Sumi Kakati</t>
+          <t>Mamoni Hazarika</t>
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr"/>
       <c r="I116" s="2" t="inlineStr"/>
       <c r="J116" s="3" t="n">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="L116" s="2" t="inlineStr"/>
-      <c r="M116" s="3" t="n">
-        <v>93</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="L116" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr"/>
       <c r="N116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
@@ -4695,31 +4695,31 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Jyotirmoy Sarmah</t>
+          <t>Mamoni Talukdar</t>
         </is>
       </c>
       <c r="D117" s="3" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr"/>
       <c r="I117" s="2" t="inlineStr"/>
       <c r="J117" s="3" t="n">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="K117" s="3" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="L117" s="2" t="inlineStr"/>
       <c r="M117" s="2" t="inlineStr"/>
       <c r="N117" s="3" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
     </row>
     <row r="118">
@@ -4733,30 +4733,30 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Mitali Baruah</t>
+          <t>Partha Saikia</t>
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr"/>
       <c r="I118" s="2" t="inlineStr"/>
       <c r="J118" s="3" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L118" s="2" t="inlineStr"/>
       <c r="M118" s="3" t="n">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="N118" s="2" t="inlineStr"/>
     </row>
@@ -4771,31 +4771,31 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Nayan Choudhury</t>
+          <t>Pranjal Rabha</t>
         </is>
       </c>
       <c r="D119" s="3" t="n">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr"/>
       <c r="I119" s="2" t="inlineStr"/>
       <c r="J119" s="3" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K119" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="L119" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="M119" s="2" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="L119" s="2" t="inlineStr"/>
+      <c r="M119" s="3" t="n">
+        <v>52</v>
+      </c>
       <c r="N119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
@@ -4809,31 +4809,31 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Dipankar Das</t>
+          <t>Juri Rabha</t>
         </is>
       </c>
       <c r="D120" s="3" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr"/>
       <c r="I120" s="2" t="inlineStr"/>
       <c r="J120" s="3" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K120" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="L120" s="2" t="inlineStr"/>
-      <c r="M120" s="3" t="n">
-        <v>43</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="L120" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr"/>
       <c r="N120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
@@ -4847,30 +4847,30 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Rupam Kakati</t>
+          <t>Rahul Kalita</t>
         </is>
       </c>
       <c r="D121" s="3" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G121" s="2" t="inlineStr"/>
       <c r="H121" s="2" t="inlineStr"/>
       <c r="I121" s="2" t="inlineStr"/>
       <c r="J121" s="3" t="n">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="L121" s="2" t="inlineStr"/>
       <c r="M121" s="3" t="n">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="N121" s="2" t="inlineStr"/>
     </row>
@@ -4885,31 +4885,31 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Dimpi Das</t>
+          <t>Gitika Kakati</t>
         </is>
       </c>
       <c r="D122" s="3" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="G122" s="2" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr"/>
       <c r="I122" s="2" t="inlineStr"/>
       <c r="J122" s="3" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="K122" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="L122" s="2" t="inlineStr"/>
-      <c r="M122" s="3" t="n">
-        <v>78</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="L122" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="M122" s="2" t="inlineStr"/>
       <c r="N122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
@@ -4923,31 +4923,31 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Himangshu Talukdar</t>
+          <t>Nayan Boro</t>
         </is>
       </c>
       <c r="D123" s="3" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>34</v>
+        <v>93</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="G123" s="2" t="inlineStr"/>
       <c r="H123" s="2" t="inlineStr"/>
       <c r="I123" s="2" t="inlineStr"/>
       <c r="J123" s="3" t="n">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="K123" s="3" t="n">
-        <v>74</v>
-      </c>
-      <c r="L123" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="M123" s="2" t="inlineStr"/>
+        <v>72</v>
+      </c>
+      <c r="L123" s="2" t="inlineStr"/>
+      <c r="M123" s="3" t="n">
+        <v>44</v>
+      </c>
       <c r="N123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
@@ -4961,32 +4961,32 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Jyotirmoy Nath</t>
+          <t>Utpal Hazarika</t>
         </is>
       </c>
       <c r="D124" s="3" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G124" s="2" t="inlineStr"/>
       <c r="H124" s="2" t="inlineStr"/>
       <c r="I124" s="2" t="inlineStr"/>
       <c r="J124" s="3" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>86</v>
-      </c>
-      <c r="L124" s="2" t="inlineStr"/>
+        <v>52</v>
+      </c>
+      <c r="L124" s="3" t="n">
+        <v>57</v>
+      </c>
       <c r="M124" s="2" t="inlineStr"/>
-      <c r="N124" s="3" t="n">
-        <v>87</v>
-      </c>
+      <c r="N124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -4999,30 +4999,30 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Barnali Rabha</t>
+          <t>Sourav Sarmah</t>
         </is>
       </c>
       <c r="D125" s="3" t="n">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="G125" s="2" t="inlineStr"/>
       <c r="H125" s="2" t="inlineStr"/>
       <c r="I125" s="2" t="inlineStr"/>
       <c r="J125" s="3" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="L125" s="2" t="inlineStr"/>
       <c r="M125" s="3" t="n">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="N125" s="2" t="inlineStr"/>
     </row>
@@ -5037,31 +5037,31 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Mitali Deka</t>
+          <t>Mintu Bhattacharya</t>
         </is>
       </c>
       <c r="D126" s="3" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr"/>
       <c r="I126" s="2" t="inlineStr"/>
       <c r="J126" s="3" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K126" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="L126" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="M126" s="2" t="inlineStr"/>
+        <v>71</v>
+      </c>
+      <c r="L126" s="2" t="inlineStr"/>
+      <c r="M126" s="3" t="n">
+        <v>57</v>
+      </c>
       <c r="N126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
@@ -5075,31 +5075,31 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Mitali Medhi</t>
+          <t>Dimpi Medhi</t>
         </is>
       </c>
       <c r="D127" s="3" t="n">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="G127" s="2" t="inlineStr"/>
       <c r="H127" s="2" t="inlineStr"/>
       <c r="I127" s="2" t="inlineStr"/>
       <c r="J127" s="3" t="n">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="K127" s="3" t="n">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="L127" s="2" t="inlineStr"/>
       <c r="M127" s="2" t="inlineStr"/>
       <c r="N127" s="3" t="n">
-        <v>80</v>
+        <v>51</v>
       </c>
     </row>
     <row r="128">
@@ -5113,14 +5113,14 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Juri Deka</t>
+          <t>Kaushik Das</t>
         </is>
       </c>
       <c r="D128" s="3" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="F128" s="3" t="n">
         <v>54</v>
@@ -5129,16 +5129,16 @@
       <c r="H128" s="2" t="inlineStr"/>
       <c r="I128" s="2" t="inlineStr"/>
       <c r="J128" s="3" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="K128" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="L128" s="2" t="inlineStr"/>
+        <v>88</v>
+      </c>
+      <c r="L128" s="3" t="n">
+        <v>78</v>
+      </c>
       <c r="M128" s="2" t="inlineStr"/>
-      <c r="N128" s="3" t="n">
-        <v>51</v>
-      </c>
+      <c r="N128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -5151,30 +5151,30 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Utpal Das</t>
+          <t>Sangita Talukdar</t>
         </is>
       </c>
       <c r="D129" s="3" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="G129" s="2" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr"/>
       <c r="I129" s="2" t="inlineStr"/>
       <c r="J129" s="3" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K129" s="3" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="L129" s="2" t="inlineStr"/>
       <c r="M129" s="3" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="N129" s="2" t="inlineStr"/>
     </row>
@@ -5189,31 +5189,31 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Mitali Sharma</t>
+          <t>Hirak Gogoi</t>
         </is>
       </c>
       <c r="D130" s="3" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr"/>
       <c r="I130" s="2" t="inlineStr"/>
       <c r="J130" s="3" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="K130" s="3" t="n">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="L130" s="2" t="inlineStr"/>
       <c r="M130" s="2" t="inlineStr"/>
       <c r="N130" s="3" t="n">
-        <v>83</v>
+        <v>29</v>
       </c>
     </row>
     <row r="131">
@@ -5227,29 +5227,29 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Juri Saikia</t>
+          <t>Mintu Deka</t>
         </is>
       </c>
       <c r="D131" s="3" t="n">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="G131" s="2" t="inlineStr"/>
       <c r="H131" s="2" t="inlineStr"/>
       <c r="I131" s="2" t="inlineStr"/>
       <c r="J131" s="3" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="K131" s="3" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="L131" s="3" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="M131" s="2" t="inlineStr"/>
       <c r="N131" s="2" t="inlineStr"/>

--- a/results/onxxgawftv.xlsx
+++ b/results/onxxgawftv.xlsx
@@ -443,13 +443,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N131"/>
+  <dimension ref="A1:O131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
@@ -460,6 +460,8 @@
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,55 +482,60 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>DOB</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Assamese</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Art &amp; Craft</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>EVS</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Hindi</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Science</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Social Science</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Elective: Hindi</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Elective: Sanskrit</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Elective: Adv. Mathematics</t>
         </is>
@@ -548,11 +555,13 @@
           <t>Hirak Deka</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>10-11-2022</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>70</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>59</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>63</v>
@@ -560,13 +569,16 @@
       <c r="G2" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="H2" s="3" t="n">
+        <v>22</v>
+      </c>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -579,28 +591,33 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Mamoni Deka</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>66</v>
+          <t>Kaushik Boro</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>12-07-2022</t>
+        </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>28</v>
+      </c>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -613,28 +630,33 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Dipankar Saikia</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n">
+          <t>Himangshu Gogoi</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>06-02-2022</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="H4" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -647,28 +669,33 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Hirak Nath</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>54</v>
+          <t>Barnali Hazarika</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>04-02-2022</t>
+        </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>78</v>
+      </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -681,28 +708,33 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Himangshu Kalita</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
+          <t>Mitali Talukdar</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>02-10-2022</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>78</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -715,28 +747,33 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Mitali Talukdar</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>38</v>
+          <t>Mamoni Bhattacharya</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>17-01-2022</t>
+        </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
+        <v>52</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>19</v>
+      </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -749,28 +786,33 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Mamoni Bhattacharya</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>38</v>
+          <t>Nirupama Boro</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>26-10-2022</t>
+        </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>43</v>
+      </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -783,28 +825,33 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nirupama Boro</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>48</v>
+          <t>Rimjim Das</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>01-07-2022</t>
+        </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr"/>
+        <v>89</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>96</v>
+      </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -817,28 +864,33 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Rimjim Das</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>19</v>
+          <t>Rahul Gogoi</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>19-08-2022</t>
+        </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>45</v>
+      </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -851,28 +903,33 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Rituparna Deka</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>86</v>
+          <t>Partha Kakati</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>22-02-2022</t>
+        </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
+        <v>94</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>90</v>
+      </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -885,28 +942,33 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Juri Boro</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>98</v>
+          <t>Dimpi Das</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>01-08-2021</t>
+        </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>54</v>
+      </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -919,28 +981,33 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Dimpi Gogoi</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="n">
+          <t>Sumi Sharma</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>14-09-2021</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="H13" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -953,28 +1020,33 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Himangshu Saikia</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>18</v>
+          <t>Karabi Choudhury</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>24-11-2021</t>
+        </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
+        <v>89</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>68</v>
+      </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -987,28 +1059,33 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Abhijit Kalita</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>52</v>
+          <t>Sumi Deka</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>12-09-2021</t>
+        </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
+        <v>88</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>94</v>
+      </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1021,28 +1098,33 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Mintu Medhi</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>96</v>
+          <t>Kangkan Baruah</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>04-08-2021</t>
+        </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>29</v>
+      </c>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1055,28 +1137,33 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Chayan Boro</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>94</v>
+          <t>Sourav Medhi</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>05-09-2021</t>
+        </is>
       </c>
       <c r="E17" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="F17" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>46</v>
-      </c>
       <c r="G17" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="H17" s="2" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>67</v>
+      </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1089,28 +1176,33 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Rahul Gogoi</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>67</v>
+          <t>Dimpi Nath</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>08-10-2021</t>
+        </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
+        <v>91</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>44</v>
+      </c>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1123,28 +1215,33 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Abhijit Saikia</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>93</v>
+          <t>Rupam Rabha</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>02-01-2021</t>
+        </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
+        <v>53</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>90</v>
+      </c>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1157,28 +1254,33 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Aarav Bhattacharya</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="n">
+          <t>Dipankar Saikia</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>01-07-2021</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="G20" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E20" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
+      <c r="H20" s="3" t="n">
+        <v>88</v>
+      </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1191,28 +1293,33 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Bikash Hazarika</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>63</v>
+          <t>Mitali Kalita</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>05-08-2021</t>
+        </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
+        <v>81</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>89</v>
+      </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1225,28 +1332,33 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Aarav Das</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>59</v>
+          <t>Mitali Nath</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>24-12-2020</t>
+        </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
+        <v>37</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>35</v>
+      </c>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1259,28 +1371,33 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Dipankar Baruah</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>85</v>
+          <t>Kangkan Hazarika</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>14-11-2020</t>
+        </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
+        <v>51</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>76</v>
+      </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1293,28 +1410,33 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Ankita Gogoi</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>63</v>
+          <t>Dimpi Choudhury</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>03-08-2020</t>
+        </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>23</v>
+      </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1327,28 +1449,33 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Kangkan Hazarika</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>86</v>
+          <t>Abhijit Deka</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>01-03-2020</t>
+        </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="H25" s="2" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>53</v>
+      </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1361,28 +1488,33 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Ankita Mahanta</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>47</v>
+          <t>Hirak Boro</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>28-02-2020</t>
+        </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>37</v>
+      </c>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1395,28 +1527,33 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Juri Dutta</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="n">
+          <t>Rupam Bhattacharya</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>23-11-2020</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="G27" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="E27" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="H27" s="2" t="inlineStr"/>
+      <c r="H27" s="3" t="n">
+        <v>49</v>
+      </c>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1429,28 +1566,33 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Himangshu Choudhury</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>47</v>
+          <t>Pooja Talukdar</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>07-01-2020</t>
+        </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>75</v>
+      </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1463,28 +1605,33 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Utpal Nath</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>83</v>
+          <t>Rahul Nath</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>11-07-2020</t>
+        </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>72</v>
+      </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1497,28 +1644,33 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Pranjal Talukdar</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>71</v>
+          <t>Jyotirmoy Das</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>12-09-2020</t>
+        </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
+        <v>87</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>94</v>
+      </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1531,28 +1683,33 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Nayan Kalita</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>20</v>
+          <t>Mamoni Baruah</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>09-08-2020</t>
+        </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1565,30 +1722,35 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Ankita Sarmah</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>62</v>
+          <t>Nayan Medhi</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>25-11-2019</t>
+        </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="I32" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr"/>
+      <c r="J32" s="3" t="n">
+        <v>34</v>
+      </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1601,30 +1763,35 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Mamoni Das</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>92</v>
+          <t>Pallabi Das</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>19-04-2019</t>
+        </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="3" t="n">
-        <v>49</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="3" t="n">
-        <v>69</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>21</v>
+      </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1637,30 +1804,35 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Kaushik Mahanta</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>74</v>
+          <t>Mamoni Choudhury</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>16-12-2019</t>
+        </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="3" t="n">
-        <v>59</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>79</v>
+      </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1673,30 +1845,35 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Pranjal Choudhury</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>37</v>
+          <t>Manash Baruah</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>22-11-2019</t>
+        </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="3" t="n">
-        <v>34</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>85</v>
+      </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1709,30 +1886,35 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Jyotirmoy Hazarika</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>66</v>
+          <t>Partha Boro</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>18-05-2019</t>
+        </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="3" t="n">
-        <v>49</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>43</v>
+      </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1745,30 +1927,35 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Mamoni Choudhury</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>94</v>
+          <t>Hirak Mahanta</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>02-01-2019</t>
+        </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="3" t="n">
-        <v>34</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr"/>
+        <v>51</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>69</v>
+      </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1781,30 +1968,35 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Trishna Talukdar</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>80</v>
+          <t>Chayan Choudhury</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>15-10-2019</t>
+        </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="3" t="n">
-        <v>54</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>68</v>
+      </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1817,30 +2009,35 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Rupam Dutta</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>66</v>
+          <t>Kaushik Bhattacharya</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>07-09-2019</t>
+        </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="3" t="n">
-        <v>22</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr"/>
+        <v>63</v>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>78</v>
+      </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1853,30 +2050,35 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Hirak Mahanta</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>27</v>
+          <t>Dipankar Gogoi</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>29-06-2019</t>
+        </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>57</v>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="3" t="n">
-        <v>26</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr"/>
+        <v>56</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>85</v>
+      </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1889,30 +2091,35 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Gitika Nath</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>89</v>
+          <t>Manash Mahanta</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>14-08-2019</t>
+        </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="3" t="n">
-        <v>74</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr"/>
+        <v>35</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>54</v>
+      </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1925,30 +2132,35 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Rimjim Kakati</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>85</v>
+          <t>Trishna Saikia</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>03-03-2018</t>
+        </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="3" t="n">
-        <v>58</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr"/>
+        <v>51</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>34</v>
+      </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1961,30 +2173,35 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Karabi Bora</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>21</v>
+          <t>Sumi Saikia</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>15-08-2018</t>
+        </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="3" t="n">
         <v>88</v>
       </c>
+      <c r="G43" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr"/>
+        <v>87</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>92</v>
+      </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1997,30 +2214,35 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Kasturi Bhattacharya</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>98</v>
+          <t>Pooja Kakati</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>03-12-2018</t>
+        </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="3" t="n">
-        <v>81</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr"/>
+        <v>79</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>26</v>
+      </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2033,30 +2255,35 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Partha Boro</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>19</v>
+          <t>Pranjal Deka</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>27-09-2018</t>
+        </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="3" t="n">
-        <v>54</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>27</v>
+      </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2069,30 +2296,35 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Rimjim Bora</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>45</v>
+          <t>Juri Gogoi</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>04-09-2018</t>
+        </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="J46" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="I46" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2105,30 +2337,35 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Sumi Saikia</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>92</v>
+          <t>Rimjim Hazarika</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>22-10-2018</t>
+        </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="3" t="n">
-        <v>87</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="J47" s="2" t="inlineStr"/>
+        <v>94</v>
+      </c>
+      <c r="J47" s="3" t="n">
+        <v>44</v>
+      </c>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2141,30 +2378,35 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Pooja Kakati</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="n">
-        <v>44</v>
+          <t>Priya Dutta</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>16-09-2018</t>
+        </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="3" t="n">
-        <v>55</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr"/>
+        <v>63</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>42</v>
+      </c>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2177,30 +2419,35 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Sumi Kalita</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="n">
-        <v>71</v>
+          <t>Juri Boro</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>21-01-2018</t>
+        </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="3" t="n">
-        <v>83</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="J49" s="3" t="n">
+        <v>38</v>
+      </c>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2213,30 +2460,35 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Barnali Kakati</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="n">
-        <v>27</v>
+          <t>Ankita Nath</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>15-09-2018</t>
+        </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="3" t="n">
-        <v>94</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>40</v>
+      </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2249,30 +2501,35 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Partha Gogoi</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="n">
-        <v>18</v>
+          <t>Pooja Hazarika</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>19-10-2018</t>
+        </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="3" t="n">
-        <v>57</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="J51" s="2" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>98</v>
+      </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2285,30 +2542,35 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Mamoni Mahanta</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="n">
-        <v>42</v>
+          <t>Ankita Kakati</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>19-07-2017</t>
+        </is>
       </c>
       <c r="E52" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="J52" s="3" t="n">
         <v>95</v>
       </c>
-      <c r="F52" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="I52" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2321,30 +2583,35 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Dimpi Mahanta</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="n">
-        <v>93</v>
+          <t>Rupam Deka</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>16-08-2017</t>
+        </is>
       </c>
       <c r="E53" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="F53" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="I53" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="J53" s="2" t="inlineStr"/>
+      <c r="J53" s="3" t="n">
+        <v>66</v>
+      </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2357,30 +2624,35 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Priya Dutta</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="n">
-        <v>53</v>
+          <t>Manash Bora</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>14-03-2017</t>
+        </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="3" t="n">
-        <v>82</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="3" t="n">
-        <v>74</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>47</v>
+      </c>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2393,30 +2665,35 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Karabi Kakati</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="n">
-        <v>78</v>
+          <t>Anaya Kakati</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>07-10-2017</t>
+        </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="F55" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="G55" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="3" t="n">
-        <v>88</v>
-      </c>
+      <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="J55" s="2" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>43</v>
+      </c>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2429,30 +2706,35 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Jyotirmoy Nath</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="n">
-        <v>44</v>
+          <t>Jyotirmoy Hazarika</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>25-04-2017</t>
+        </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="3" t="n">
-        <v>96</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr"/>
+        <v>67</v>
+      </c>
+      <c r="J56" s="3" t="n">
+        <v>85</v>
+      </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2465,30 +2747,35 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Sangita Sharma</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="n">
-        <v>70</v>
+          <t>Sumi Dutta</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>05-05-2017</t>
+        </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="3" t="n">
-        <v>40</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="H57" s="2" t="inlineStr"/>
       <c r="I57" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J57" s="2" t="inlineStr"/>
+        <v>82</v>
+      </c>
+      <c r="J57" s="3" t="n">
+        <v>94</v>
+      </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2501,30 +2788,35 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Gitika Baruah</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="n">
-        <v>77</v>
+          <t>Rupam Gogoi</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>30-05-2017</t>
+        </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="3" t="n">
-        <v>70</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr"/>
+        <v>87</v>
+      </c>
+      <c r="J58" s="3" t="n">
+        <v>41</v>
+      </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2537,30 +2829,35 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Ankita Nath</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="n">
-        <v>68</v>
+          <t>Pooja Sarmah</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>24-01-2017</t>
+        </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="3" t="n">
-        <v>75</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="J59" s="2" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="J59" s="3" t="n">
+        <v>97</v>
+      </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr"/>
       <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2573,30 +2870,35 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Rituparna Mahanta</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="n">
-        <v>81</v>
+          <t>Kangkan Sarmah</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>07-09-2017</t>
+        </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="3" t="n">
-        <v>50</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="H60" s="2" t="inlineStr"/>
       <c r="I60" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr"/>
+        <v>82</v>
+      </c>
+      <c r="J60" s="3" t="n">
+        <v>90</v>
+      </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2609,30 +2911,35 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Priya Mahanta</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="n">
-        <v>43</v>
+          <t>Chayan Dutta</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>02-10-2017</t>
+        </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="3" t="n">
-        <v>81</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="J61" s="2" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>76</v>
+      </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2645,30 +2952,35 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Pooja Hazarika</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="n">
-        <v>95</v>
+          <t>Himangshu Dutta</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>31-03-2016</t>
+        </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>78</v>
-      </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="3" t="n">
-        <v>63</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="J62" s="3" t="n">
+        <v>47</v>
+      </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2681,30 +2993,35 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Ankita Boro</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="n">
-        <v>48</v>
+          <t>Rimjim Bhattacharya</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>31-12-2016</t>
+        </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="3" t="n">
-        <v>57</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="3" t="n">
-        <v>77</v>
-      </c>
-      <c r="J63" s="2" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="J63" s="3" t="n">
+        <v>84</v>
+      </c>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr"/>
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2717,30 +3034,35 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Partha Rabha</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="n">
-        <v>78</v>
+          <t>Chayan Bhattacharya</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>19-05-2016</t>
+        </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="F64" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="3" t="n">
-        <v>61</v>
-      </c>
+      <c r="G64" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr"/>
+        <v>95</v>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>97</v>
+      </c>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr"/>
       <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2753,30 +3075,35 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Barnali Hazarika</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="n">
-        <v>37</v>
+          <t>Aarav Sarmah</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>14-11-2016</t>
+        </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="3" t="n">
-        <v>27</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="J65" s="3" t="n">
+        <v>85</v>
+      </c>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="2" t="inlineStr"/>
       <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2789,30 +3116,35 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Rimjim Sarmah</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="n">
+          <t>Dimpi Rabha</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>17-02-2016</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="E66" s="3" t="n">
-        <v>82</v>
-      </c>
       <c r="F66" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="3" t="n">
-        <v>95</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr"/>
       <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2825,30 +3157,35 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Sourav Gogoi</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="n">
+          <t>Pranjal Saikia</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>24-10-2016</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="E67" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="I67" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr"/>
+      <c r="J67" s="3" t="n">
+        <v>31</v>
+      </c>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="2" t="inlineStr"/>
       <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -2861,30 +3198,35 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Anaya Kakati</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="n">
-        <v>43</v>
+          <t>Nayan Boro</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>19-05-2016</t>
+        </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="3" t="n">
-        <v>72</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr"/>
+        <v>93</v>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>91</v>
+      </c>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr"/>
       <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2897,30 +3239,35 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Manash Medhi</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="n">
-        <v>74</v>
+          <t>Bikash Deka</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>16-04-2016</t>
+        </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="3" t="n">
-        <v>88</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="H69" s="2" t="inlineStr"/>
       <c r="I69" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="J69" s="2" t="inlineStr"/>
+        <v>82</v>
+      </c>
+      <c r="J69" s="3" t="n">
+        <v>98</v>
+      </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr"/>
       <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2933,30 +3280,35 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Pranjal Baruah</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="n">
-        <v>67</v>
+          <t>Himangshu Bora</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>21-03-2016</t>
+        </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="3" t="n">
-        <v>70</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="J70" s="3" t="n">
+        <v>47</v>
+      </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr"/>
       <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -2969,30 +3321,35 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Dipankar Sarmah</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="n">
-        <v>51</v>
+          <t>Mitali Baruah</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>13-05-2016</t>
+        </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>69</v>
-      </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="3" t="n">
-        <v>82</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="J71" s="3" t="n">
+        <v>16</v>
+      </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -3005,30 +3362,35 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Rupam Gogoi</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="n">
-        <v>82</v>
+          <t>Jyotirmoy Choudhury</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>12-07-2015</t>
+        </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="3" t="n">
-        <v>73</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr"/>
+        <v>89</v>
+      </c>
+      <c r="J72" s="3" t="n">
+        <v>79</v>
+      </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -3041,30 +3403,35 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Anaya Kalita</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="n">
-        <v>62</v>
+          <t>Mitali Boro</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>05-11-2015</t>
+        </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="3" t="n">
-        <v>87</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="J73" s="2" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="J73" s="3" t="n">
+        <v>49</v>
+      </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -3077,30 +3444,35 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Rituparna Saikia</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="n">
-        <v>62</v>
+          <t>Bikash Nath</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>11-02-2015</t>
+        </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="3" t="n">
-        <v>54</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="J74" s="3" t="n">
+        <v>81</v>
+      </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -3113,30 +3485,35 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Mitali Hazarika</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="n">
-        <v>61</v>
+          <t>Sumi Boro</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>28-12-2015</t>
+        </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="3" t="n">
-        <v>82</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="J75" s="2" t="inlineStr"/>
+        <v>56</v>
+      </c>
+      <c r="J75" s="3" t="n">
+        <v>45</v>
+      </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr"/>
       <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -3149,30 +3526,35 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Chayan Dutta</t>
-        </is>
-      </c>
-      <c r="D76" s="3" t="n">
-        <v>96</v>
+          <t>Priya Sarmah</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>21-03-2015</t>
+        </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="3" t="n">
-        <v>67</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr"/>
+        <v>53</v>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>91</v>
+      </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr"/>
       <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -3185,30 +3567,35 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Dimpi Saikia</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="n">
-        <v>82</v>
+          <t>Partha Bora</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>23-10-2015</t>
+        </is>
       </c>
       <c r="E77" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="J77" s="3" t="n">
         <v>71</v>
       </c>
-      <c r="F77" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="I77" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr"/>
       <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -3221,30 +3608,35 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Mamoni Saikia</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="n">
-        <v>87</v>
+          <t>Aarav Bora</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>04-06-2015</t>
+        </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="3" t="n">
-        <v>55</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="H78" s="2" t="inlineStr"/>
       <c r="I78" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>78</v>
+      </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr"/>
       <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -3257,30 +3649,35 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Nirupama Medhi</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="n">
-        <v>68</v>
+          <t>Mintu Bora</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>19-02-2015</t>
+        </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>77</v>
-      </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="3" t="n">
-        <v>76</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="H79" s="2" t="inlineStr"/>
       <c r="I79" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="J79" s="2" t="inlineStr"/>
+        <v>71</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>85</v>
+      </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr"/>
       <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -3293,30 +3690,35 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Aarav Sarmah</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="n">
-        <v>61</v>
+          <t>Utpal Mahanta</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>02-06-2015</t>
+        </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="3" t="n">
-        <v>64</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="H80" s="2" t="inlineStr"/>
       <c r="I80" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>58</v>
+      </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr"/>
       <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -3329,30 +3731,35 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Himangshu Dutta</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="n">
-        <v>46</v>
+          <t>Anaya Saikia</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>06-03-2015</t>
+        </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="3" t="n">
-        <v>69</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr"/>
+        <v>94</v>
+      </c>
+      <c r="J81" s="3" t="n">
+        <v>48</v>
+      </c>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr"/>
       <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -3365,32 +3772,37 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Anaya Rabha</t>
-        </is>
-      </c>
-      <c r="D82" s="3" t="n">
-        <v>21</v>
+          <t>Abhijit Kalita</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>20-04-2014</t>
+        </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="F82" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="K82" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr"/>
-      <c r="I82" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="J82" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="K82" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="L82" s="2" t="inlineStr"/>
+      <c r="L82" s="3" t="n">
+        <v>64</v>
+      </c>
       <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -3403,32 +3815,37 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Jyotirmoy Kalita</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="n">
-        <v>73</v>
+          <t>Rima Bora</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>01-05-2014</t>
+        </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="G83" s="2" t="inlineStr"/>
+        <v>72</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>59</v>
+      </c>
       <c r="H83" s="2" t="inlineStr"/>
-      <c r="I83" s="3" t="n">
-        <v>56</v>
-      </c>
+      <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="3" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="K83" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="L83" s="2" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="L83" s="3" t="n">
+        <v>63</v>
+      </c>
       <c r="M83" s="2" t="inlineStr"/>
       <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -3441,32 +3858,37 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Abhijit Choudhury</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="n">
-        <v>46</v>
+          <t>Mamoni Dutta</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>15-06-2014</t>
+        </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="G84" s="2" t="inlineStr"/>
+        <v>53</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>54</v>
+      </c>
       <c r="H84" s="2" t="inlineStr"/>
-      <c r="I84" s="3" t="n">
-        <v>44</v>
-      </c>
+      <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="3" t="n">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="L84" s="2" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="L84" s="3" t="n">
+        <v>77</v>
+      </c>
       <c r="M84" s="2" t="inlineStr"/>
       <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -3479,32 +3901,37 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Pallabi Dutta</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="n">
-        <v>76</v>
+          <t>Barnali Choudhury</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>09-06-2014</t>
+        </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="G85" s="2" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>61</v>
+      </c>
       <c r="H85" s="2" t="inlineStr"/>
-      <c r="I85" s="3" t="n">
-        <v>46</v>
-      </c>
+      <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="3" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="L85" s="2" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="L85" s="3" t="n">
+        <v>78</v>
+      </c>
       <c r="M85" s="2" t="inlineStr"/>
       <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -3517,11 +3944,13 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Chayan Sarmah</t>
-        </is>
-      </c>
-      <c r="D86" s="3" t="n">
-        <v>44</v>
+          <t>Rupam Medhi</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>01-07-2014</t>
+        </is>
       </c>
       <c r="E86" s="3" t="n">
         <v>41</v>
@@ -3529,20 +3958,23 @@
       <c r="F86" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
+      <c r="G86" s="3" t="n">
+        <v>83</v>
+      </c>
       <c r="H86" s="2" t="inlineStr"/>
-      <c r="I86" s="3" t="n">
-        <v>82</v>
-      </c>
+      <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="3" t="n">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="L86" s="2" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="L86" s="3" t="n">
+        <v>94</v>
+      </c>
       <c r="M86" s="2" t="inlineStr"/>
       <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -3555,32 +3987,37 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Rima Medhi</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="n">
-        <v>58</v>
+          <t>Kasturi Sarmah</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>09-07-2014</t>
+        </is>
       </c>
       <c r="E87" s="3" t="n">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>77</v>
-      </c>
-      <c r="G87" s="2" t="inlineStr"/>
+        <v>56</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>49</v>
+      </c>
       <c r="H87" s="2" t="inlineStr"/>
-      <c r="I87" s="3" t="n">
-        <v>79</v>
-      </c>
+      <c r="I87" s="2" t="inlineStr"/>
       <c r="J87" s="3" t="n">
         <v>94</v>
       </c>
       <c r="K87" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="L87" s="2" t="inlineStr"/>
+        <v>87</v>
+      </c>
+      <c r="L87" s="3" t="n">
+        <v>42</v>
+      </c>
       <c r="M87" s="2" t="inlineStr"/>
       <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -3593,32 +4030,37 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Pallabi Bhattacharya</t>
-        </is>
-      </c>
-      <c r="D88" s="3" t="n">
-        <v>60</v>
+          <t>Rima Rabha</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>15-12-2014</t>
+        </is>
       </c>
       <c r="E88" s="3" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="G88" s="2" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>51</v>
+      </c>
       <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="3" t="n">
-        <v>74</v>
-      </c>
+      <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="3" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="L88" s="2" t="inlineStr"/>
+        <v>67</v>
+      </c>
+      <c r="L88" s="3" t="n">
+        <v>72</v>
+      </c>
       <c r="M88" s="2" t="inlineStr"/>
       <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -3631,32 +4073,37 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Rupam Choudhury</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="n">
-        <v>64</v>
+          <t>Utpal Baruah</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>22-11-2014</t>
+        </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F89" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr"/>
-      <c r="I89" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="J89" s="3" t="n">
-        <v>89</v>
-      </c>
       <c r="K89" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="L89" s="2" t="inlineStr"/>
+        <v>86</v>
+      </c>
+      <c r="L89" s="3" t="n">
+        <v>62</v>
+      </c>
       <c r="M89" s="2" t="inlineStr"/>
       <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -3669,32 +4116,37 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Abhijit Bora</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="n">
+          <t>Hirak Baruah</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>22-03-2014</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="K90" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="L90" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="E90" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="F90" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr"/>
-      <c r="I90" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="J90" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="K90" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="L90" s="2" t="inlineStr"/>
       <c r="M90" s="2" t="inlineStr"/>
       <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -3707,32 +4159,37 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Barnali Deka</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="n">
-        <v>48</v>
+          <t>Anaya Choudhury</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>31-05-2014</t>
+        </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="G91" s="2" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>76</v>
+      </c>
       <c r="H91" s="2" t="inlineStr"/>
-      <c r="I91" s="3" t="n">
-        <v>81</v>
-      </c>
+      <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="3" t="n">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="L91" s="2" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="L91" s="3" t="n">
+        <v>63</v>
+      </c>
       <c r="M91" s="2" t="inlineStr"/>
       <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -3745,32 +4202,37 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Sumi Boro</t>
-        </is>
-      </c>
-      <c r="D92" s="3" t="n">
-        <v>87</v>
+          <t>Karabi Saikia</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>22-01-2013</t>
+        </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="G92" s="2" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>74</v>
+      </c>
       <c r="H92" s="2" t="inlineStr"/>
-      <c r="I92" s="3" t="n">
-        <v>77</v>
-      </c>
+      <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" s="3" t="n">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="L92" s="2" t="inlineStr"/>
+        <v>93</v>
+      </c>
+      <c r="L92" s="3" t="n">
+        <v>90</v>
+      </c>
       <c r="M92" s="2" t="inlineStr"/>
       <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -3783,32 +4245,37 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Rahul Medhi</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="n">
-        <v>50</v>
+          <t>Nayan Saikia</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>30-01-2013</t>
+        </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="G93" s="2" t="inlineStr"/>
+        <v>66</v>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>98</v>
+      </c>
       <c r="H93" s="2" t="inlineStr"/>
-      <c r="I93" s="3" t="n">
-        <v>52</v>
-      </c>
+      <c r="I93" s="2" t="inlineStr"/>
       <c r="J93" s="3" t="n">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="K93" s="3" t="n">
-        <v>74</v>
-      </c>
-      <c r="L93" s="2" t="inlineStr"/>
+        <v>66</v>
+      </c>
+      <c r="L93" s="3" t="n">
+        <v>71</v>
+      </c>
       <c r="M93" s="2" t="inlineStr"/>
       <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -3821,32 +4288,37 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Priya Hazarika</t>
-        </is>
-      </c>
-      <c r="D94" s="3" t="n">
-        <v>95</v>
+          <t>Aarav Talukdar</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>08-09-2013</t>
+        </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="G94" s="2" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>97</v>
+      </c>
       <c r="H94" s="2" t="inlineStr"/>
-      <c r="I94" s="3" t="n">
-        <v>78</v>
-      </c>
+      <c r="I94" s="2" t="inlineStr"/>
       <c r="J94" s="3" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K94" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="L94" s="2" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="L94" s="3" t="n">
+        <v>96</v>
+      </c>
       <c r="M94" s="2" t="inlineStr"/>
       <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -3859,32 +4331,37 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Rima Gogoi</t>
-        </is>
-      </c>
-      <c r="D95" s="3" t="n">
-        <v>85</v>
+          <t>Rimjim Saikia</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>18-06-2013</t>
+        </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="G95" s="2" t="inlineStr"/>
+        <v>59</v>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>48</v>
+      </c>
       <c r="H95" s="2" t="inlineStr"/>
-      <c r="I95" s="3" t="n">
-        <v>60</v>
-      </c>
+      <c r="I95" s="2" t="inlineStr"/>
       <c r="J95" s="3" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="K95" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="L95" s="2" t="inlineStr"/>
+        <v>91</v>
+      </c>
+      <c r="L95" s="3" t="n">
+        <v>49</v>
+      </c>
       <c r="M95" s="2" t="inlineStr"/>
       <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -3897,32 +4374,37 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Himangshu Hazarika</t>
-        </is>
-      </c>
-      <c r="D96" s="3" t="n">
-        <v>98</v>
+          <t>Mintu Saikia</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>04-09-2013</t>
+        </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="G96" s="2" t="inlineStr"/>
+        <v>71</v>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>55</v>
+      </c>
       <c r="H96" s="2" t="inlineStr"/>
-      <c r="I96" s="3" t="n">
-        <v>45</v>
-      </c>
+      <c r="I96" s="2" t="inlineStr"/>
       <c r="J96" s="3" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K96" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="L96" s="2" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="L96" s="3" t="n">
+        <v>80</v>
+      </c>
       <c r="M96" s="2" t="inlineStr"/>
       <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -3935,32 +4417,37 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Mintu Bora</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="n">
-        <v>50</v>
+          <t>Priya Hazarika</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>04-02-2013</t>
+        </is>
       </c>
       <c r="E97" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="K97" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="F97" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr"/>
-      <c r="I97" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="J97" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="K97" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="L97" s="2" t="inlineStr"/>
+      <c r="L97" s="3" t="n">
+        <v>73</v>
+      </c>
       <c r="M97" s="2" t="inlineStr"/>
       <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -3973,32 +4460,37 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Utpal Mahanta</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="n">
-        <v>81</v>
+          <t>Utpal Boro</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>17-10-2013</t>
+        </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="G98" s="2" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>37</v>
+      </c>
       <c r="H98" s="2" t="inlineStr"/>
-      <c r="I98" s="3" t="n">
-        <v>55</v>
-      </c>
+      <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="3" t="n">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="K98" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="L98" s="2" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="L98" s="3" t="n">
+        <v>30</v>
+      </c>
       <c r="M98" s="2" t="inlineStr"/>
       <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -4011,32 +4503,37 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Pranjal Das</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="n">
-        <v>50</v>
+          <t>Pranjal Rabha</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>04-06-2013</t>
+        </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="G99" s="2" t="inlineStr"/>
+        <v>94</v>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>65</v>
+      </c>
       <c r="H99" s="2" t="inlineStr"/>
-      <c r="I99" s="3" t="n">
-        <v>55</v>
-      </c>
+      <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="3" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="L99" s="2" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="L99" s="3" t="n">
+        <v>52</v>
+      </c>
       <c r="M99" s="2" t="inlineStr"/>
       <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -4049,32 +4546,37 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Dipankar Boro</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="n">
-        <v>69</v>
+          <t>Juri Rabha</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>19-04-2013</t>
+        </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="G100" s="2" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>12</v>
+      </c>
       <c r="H100" s="2" t="inlineStr"/>
-      <c r="I100" s="3" t="n">
-        <v>41</v>
-      </c>
+      <c r="I100" s="2" t="inlineStr"/>
       <c r="J100" s="3" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="L100" s="2" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="L100" s="3" t="n">
+        <v>22</v>
+      </c>
       <c r="M100" s="2" t="inlineStr"/>
       <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -4087,32 +4589,37 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Rima Bora</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="n">
-        <v>98</v>
+          <t>Rimjim Kalita</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>09-06-2013</t>
+        </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="G101" s="2" t="inlineStr"/>
+        <v>84</v>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>43</v>
+      </c>
       <c r="H101" s="2" t="inlineStr"/>
-      <c r="I101" s="3" t="n">
-        <v>70</v>
-      </c>
+      <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" s="3" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="L101" s="2" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="L101" s="3" t="n">
+        <v>40</v>
+      </c>
       <c r="M101" s="2" t="inlineStr"/>
       <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -4125,32 +4632,37 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Manash Hazarika</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="n">
-        <v>53</v>
+          <t>Sourav Bora</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>23-08-2012</t>
+        </is>
       </c>
       <c r="E102" s="3" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="G102" s="2" t="inlineStr"/>
+        <v>77</v>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>59</v>
+      </c>
       <c r="H102" s="2" t="inlineStr"/>
-      <c r="I102" s="3" t="n">
-        <v>27</v>
-      </c>
+      <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="3" t="n">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="K102" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="L102" s="2" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="L102" s="3" t="n">
+        <v>68</v>
+      </c>
       <c r="M102" s="2" t="inlineStr"/>
       <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -4163,32 +4675,37 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Trishna Medhi</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="n">
-        <v>64</v>
+          <t>Rahul Medhi</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>21-11-2012</t>
+        </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="G103" s="2" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>74</v>
+      </c>
       <c r="H103" s="2" t="inlineStr"/>
-      <c r="I103" s="3" t="n">
-        <v>89</v>
-      </c>
+      <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="3" t="n">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="K103" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="L103" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="L103" s="2" t="inlineStr"/>
       <c r="M103" s="2" t="inlineStr"/>
       <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -4201,32 +4718,37 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Rupam Medhi</t>
-        </is>
-      </c>
-      <c r="D104" s="3" t="n">
-        <v>44</v>
+          <t>Pallabi Hazarika</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>06-05-2012</t>
+        </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="G104" s="2" t="inlineStr"/>
+        <v>94</v>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>43</v>
+      </c>
       <c r="H104" s="2" t="inlineStr"/>
-      <c r="I104" s="3" t="n">
-        <v>83</v>
-      </c>
+      <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="3" t="n">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="K104" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="L104" s="2" t="inlineStr"/>
+        <v>92</v>
+      </c>
+      <c r="L104" s="3" t="n">
+        <v>86</v>
+      </c>
       <c r="M104" s="2" t="inlineStr"/>
       <c r="N104" s="2" t="inlineStr"/>
+      <c r="O104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -4239,32 +4761,37 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Rituparna Dutta</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="n">
-        <v>62</v>
+          <t>Hirak Kakati</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>15-08-2012</t>
+        </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="G105" s="2" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>75</v>
+      </c>
       <c r="H105" s="2" t="inlineStr"/>
-      <c r="I105" s="3" t="n">
-        <v>95</v>
-      </c>
+      <c r="I105" s="2" t="inlineStr"/>
       <c r="J105" s="3" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="K105" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="L105" s="2" t="inlineStr"/>
+        <v>72</v>
+      </c>
+      <c r="L105" s="3" t="n">
+        <v>71</v>
+      </c>
       <c r="M105" s="2" t="inlineStr"/>
       <c r="N105" s="2" t="inlineStr"/>
+      <c r="O105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -4277,32 +4804,37 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Utpal Bora</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="n">
-        <v>94</v>
+          <t>Dimpi Medhi</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>21-11-2012</t>
+        </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="G106" s="2" t="inlineStr"/>
+        <v>66</v>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>97</v>
+      </c>
       <c r="H106" s="2" t="inlineStr"/>
-      <c r="I106" s="3" t="n">
-        <v>87</v>
-      </c>
+      <c r="I106" s="2" t="inlineStr"/>
       <c r="J106" s="3" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>74</v>
-      </c>
-      <c r="L106" s="2" t="inlineStr"/>
+        <v>88</v>
+      </c>
+      <c r="L106" s="3" t="n">
+        <v>51</v>
+      </c>
       <c r="M106" s="2" t="inlineStr"/>
       <c r="N106" s="2" t="inlineStr"/>
+      <c r="O106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -4315,32 +4847,37 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Nirupama Bhattacharya</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="n">
-        <v>72</v>
+          <t>Kaushik Das</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>11-01-2012</t>
+        </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="G107" s="2" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>88</v>
+      </c>
       <c r="H107" s="2" t="inlineStr"/>
-      <c r="I107" s="3" t="n">
-        <v>59</v>
-      </c>
+      <c r="I107" s="2" t="inlineStr"/>
       <c r="J107" s="3" t="n">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="L107" s="2" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="L107" s="3" t="n">
+        <v>63</v>
+      </c>
       <c r="M107" s="2" t="inlineStr"/>
       <c r="N107" s="2" t="inlineStr"/>
+      <c r="O107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -4353,32 +4890,37 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Abhijit Deka</t>
-        </is>
-      </c>
-      <c r="D108" s="3" t="n">
-        <v>98</v>
+          <t>Dhruba Dutta</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>16-09-2012</t>
+        </is>
       </c>
       <c r="E108" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="F108" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="F108" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="G108" s="2" t="inlineStr"/>
+      <c r="G108" s="3" t="n">
+        <v>49</v>
+      </c>
       <c r="H108" s="2" t="inlineStr"/>
-      <c r="I108" s="3" t="n">
-        <v>91</v>
-      </c>
+      <c r="I108" s="2" t="inlineStr"/>
       <c r="J108" s="3" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="K108" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="L108" s="2" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="L108" s="3" t="n">
+        <v>83</v>
+      </c>
       <c r="M108" s="2" t="inlineStr"/>
       <c r="N108" s="2" t="inlineStr"/>
+      <c r="O108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -4391,32 +4933,37 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Rima Saikia</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="n">
-        <v>40</v>
+          <t>Mintu Deka</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>19-02-2012</t>
+        </is>
       </c>
       <c r="E109" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H109" s="2" t="inlineStr"/>
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="3" t="n">
         <v>52</v>
-      </c>
-      <c r="F109" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr"/>
-      <c r="I109" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="J109" s="3" t="n">
-        <v>83</v>
       </c>
       <c r="K109" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="L109" s="2" t="inlineStr"/>
+      <c r="L109" s="3" t="n">
+        <v>49</v>
+      </c>
       <c r="M109" s="2" t="inlineStr"/>
       <c r="N109" s="2" t="inlineStr"/>
+      <c r="O109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -4429,32 +4976,37 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Sangita Das</t>
-        </is>
-      </c>
-      <c r="D110" s="3" t="n">
+          <t>Trishna Hazarika</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>14-05-2012</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="E110" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="F110" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr"/>
-      <c r="I110" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="J110" s="3" t="n">
-        <v>59</v>
-      </c>
       <c r="K110" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="L110" s="2" t="inlineStr"/>
+        <v>69</v>
+      </c>
+      <c r="L110" s="3" t="n">
+        <v>55</v>
+      </c>
       <c r="M110" s="2" t="inlineStr"/>
       <c r="N110" s="2" t="inlineStr"/>
+      <c r="O110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -4467,32 +5019,37 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Abhijit Sharma</t>
-        </is>
-      </c>
-      <c r="D111" s="3" t="n">
-        <v>49</v>
+          <t>Mitali Bhattacharya</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>23-03-2012</t>
+        </is>
       </c>
       <c r="E111" s="3" t="n">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="G111" s="2" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>75</v>
+      </c>
       <c r="H111" s="2" t="inlineStr"/>
-      <c r="I111" s="3" t="n">
-        <v>93</v>
-      </c>
+      <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="3" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="L111" s="2" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="L111" s="3" t="n">
+        <v>67</v>
+      </c>
       <c r="M111" s="2" t="inlineStr"/>
       <c r="N111" s="2" t="inlineStr"/>
+      <c r="O111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -4505,31 +5062,36 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Rimjim Deka</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="n">
-        <v>90</v>
+          <t>Mintu Choudhury</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>13-09-2011</t>
+        </is>
       </c>
       <c r="E112" s="3" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="G112" s="2" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>91</v>
+      </c>
       <c r="H112" s="2" t="inlineStr"/>
       <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="3" t="n">
-        <v>51</v>
-      </c>
+      <c r="J112" s="2" t="inlineStr"/>
       <c r="K112" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="L112" s="2" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="L112" s="3" t="n">
+        <v>64</v>
+      </c>
       <c r="M112" s="2" t="inlineStr"/>
-      <c r="N112" s="3" t="n">
-        <v>98</v>
+      <c r="N112" s="2" t="inlineStr"/>
+      <c r="O112" s="3" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="113">
@@ -4543,32 +5105,37 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Utpal Sarmah</t>
-        </is>
-      </c>
-      <c r="D113" s="3" t="n">
-        <v>71</v>
+          <t>Rupam Kalita</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>05-05-2011</t>
+        </is>
       </c>
       <c r="E113" s="3" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="G113" s="2" t="inlineStr"/>
+        <v>73</v>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>91</v>
+      </c>
       <c r="H113" s="2" t="inlineStr"/>
       <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="3" t="n">
-        <v>60</v>
-      </c>
+      <c r="J113" s="2" t="inlineStr"/>
       <c r="K113" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="L113" s="2" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="L113" s="3" t="n">
+        <v>85</v>
+      </c>
       <c r="M113" s="3" t="n">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="N113" s="2" t="inlineStr"/>
+      <c r="O113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -4581,32 +5148,37 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Manash Talukdar</t>
-        </is>
-      </c>
-      <c r="D114" s="3" t="n">
-        <v>51</v>
+          <t>Kasturi Baruah</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>29-05-2011</t>
+        </is>
       </c>
       <c r="E114" s="3" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="G114" s="2" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>77</v>
+      </c>
       <c r="H114" s="2" t="inlineStr"/>
       <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="3" t="n">
-        <v>63</v>
-      </c>
+      <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="3" t="n">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="L114" s="3" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="M114" s="2" t="inlineStr"/>
-      <c r="N114" s="2" t="inlineStr"/>
+      <c r="N114" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -4619,32 +5191,37 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Trishna Kakati</t>
-        </is>
-      </c>
-      <c r="D115" s="3" t="n">
-        <v>91</v>
+          <t>Aarav Baruah</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>29-07-2011</t>
+        </is>
       </c>
       <c r="E115" s="3" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>67</v>
-      </c>
-      <c r="G115" s="2" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>80</v>
+      </c>
       <c r="H115" s="2" t="inlineStr"/>
       <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="3" t="n">
-        <v>78</v>
-      </c>
+      <c r="J115" s="2" t="inlineStr"/>
       <c r="K115" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="L115" s="2" t="inlineStr"/>
-      <c r="M115" s="3" t="n">
-        <v>73</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="L115" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="M115" s="2" t="inlineStr"/>
       <c r="N115" s="2" t="inlineStr"/>
+      <c r="O115" s="3" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -4657,32 +5234,37 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Mamoni Hazarika</t>
-        </is>
-      </c>
-      <c r="D116" s="3" t="n">
-        <v>27</v>
+          <t>Kasturi Mahanta</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>10-10-2011</t>
+        </is>
       </c>
       <c r="E116" s="3" t="n">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="G116" s="2" t="inlineStr"/>
+        <v>81</v>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>97</v>
+      </c>
       <c r="H116" s="2" t="inlineStr"/>
       <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="3" t="n">
-        <v>90</v>
-      </c>
+      <c r="J116" s="2" t="inlineStr"/>
       <c r="K116" s="3" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="M116" s="2" t="inlineStr"/>
-      <c r="N116" s="2" t="inlineStr"/>
+      <c r="N116" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -4695,31 +5277,36 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Mamoni Talukdar</t>
-        </is>
-      </c>
-      <c r="D117" s="3" t="n">
-        <v>54</v>
+          <t>Rituparna Hazarika</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>05-09-2011</t>
+        </is>
       </c>
       <c r="E117" s="3" t="n">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>78</v>
-      </c>
-      <c r="G117" s="2" t="inlineStr"/>
+        <v>63</v>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>88</v>
+      </c>
       <c r="H117" s="2" t="inlineStr"/>
       <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="3" t="n">
-        <v>56</v>
-      </c>
+      <c r="J117" s="2" t="inlineStr"/>
       <c r="K117" s="3" t="n">
-        <v>77</v>
-      </c>
-      <c r="L117" s="2" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="L117" s="3" t="n">
+        <v>57</v>
+      </c>
       <c r="M117" s="2" t="inlineStr"/>
-      <c r="N117" s="3" t="n">
-        <v>77</v>
+      <c r="N117" s="2" t="inlineStr"/>
+      <c r="O117" s="3" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="118">
@@ -4733,32 +5320,37 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Partha Saikia</t>
-        </is>
-      </c>
-      <c r="D118" s="3" t="n">
-        <v>97</v>
+          <t>Sourav Bhattacharya</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>09-08-2011</t>
+        </is>
       </c>
       <c r="E118" s="3" t="n">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="G118" s="2" t="inlineStr"/>
+        <v>82</v>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>96</v>
+      </c>
       <c r="H118" s="2" t="inlineStr"/>
       <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="3" t="n">
-        <v>91</v>
-      </c>
+      <c r="J118" s="2" t="inlineStr"/>
       <c r="K118" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="L118" s="2" t="inlineStr"/>
+        <v>86</v>
+      </c>
+      <c r="L118" s="3" t="n">
+        <v>31</v>
+      </c>
       <c r="M118" s="3" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="N118" s="2" t="inlineStr"/>
+      <c r="O118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -4771,32 +5363,37 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Pranjal Rabha</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="n">
-        <v>69</v>
+          <t>Mitali Hazarika</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>26-08-2011</t>
+        </is>
       </c>
       <c r="E119" s="3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="G119" s="2" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>81</v>
+      </c>
       <c r="H119" s="2" t="inlineStr"/>
       <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="3" t="n">
-        <v>65</v>
-      </c>
+      <c r="J119" s="2" t="inlineStr"/>
       <c r="K119" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="L119" s="2" t="inlineStr"/>
-      <c r="M119" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="N119" s="2" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="L119" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="M119" s="2" t="inlineStr"/>
+      <c r="N119" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="O119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -4809,32 +5406,37 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Juri Rabha</t>
-        </is>
-      </c>
-      <c r="D120" s="3" t="n">
-        <v>55</v>
+          <t>Partha Mahanta</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>30-10-2011</t>
+        </is>
       </c>
       <c r="E120" s="3" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="G120" s="2" t="inlineStr"/>
+        <v>83</v>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>69</v>
+      </c>
       <c r="H120" s="2" t="inlineStr"/>
       <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="3" t="n">
-        <v>41</v>
-      </c>
+      <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="3" t="n">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="L120" s="3" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="M120" s="2" t="inlineStr"/>
-      <c r="N120" s="2" t="inlineStr"/>
+      <c r="N120" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="O120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -4847,32 +5449,37 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Rahul Kalita</t>
-        </is>
-      </c>
-      <c r="D121" s="3" t="n">
-        <v>82</v>
+          <t>Pallabi Kalita</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>17-02-2011</t>
+        </is>
       </c>
       <c r="E121" s="3" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="G121" s="2" t="inlineStr"/>
+        <v>93</v>
+      </c>
+      <c r="G121" s="3" t="n">
+        <v>66</v>
+      </c>
       <c r="H121" s="2" t="inlineStr"/>
       <c r="I121" s="2" t="inlineStr"/>
-      <c r="J121" s="3" t="n">
-        <v>82</v>
-      </c>
+      <c r="J121" s="2" t="inlineStr"/>
       <c r="K121" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="L121" s="2" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="L121" s="3" t="n">
+        <v>70</v>
+      </c>
       <c r="M121" s="3" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="N121" s="2" t="inlineStr"/>
+      <c r="O121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -4885,32 +5492,37 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Gitika Kakati</t>
-        </is>
-      </c>
-      <c r="D122" s="3" t="n">
-        <v>57</v>
+          <t>Karabi Sarmah</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>06-06-2010</t>
+        </is>
       </c>
       <c r="E122" s="3" t="n">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="G122" s="2" t="inlineStr"/>
+        <v>59</v>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>62</v>
+      </c>
       <c r="H122" s="2" t="inlineStr"/>
       <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="3" t="n">
-        <v>50</v>
-      </c>
+      <c r="J122" s="2" t="inlineStr"/>
       <c r="K122" s="3" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L122" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="M122" s="2" t="inlineStr"/>
+        <v>88</v>
+      </c>
+      <c r="M122" s="3" t="n">
+        <v>85</v>
+      </c>
       <c r="N122" s="2" t="inlineStr"/>
+      <c r="O122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -4923,32 +5535,37 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Nayan Boro</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="n">
-        <v>73</v>
+          <t>Sangita Baruah</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>16-01-2010</t>
+        </is>
       </c>
       <c r="E123" s="3" t="n">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="G123" s="2" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>97</v>
+      </c>
       <c r="H123" s="2" t="inlineStr"/>
       <c r="I123" s="2" t="inlineStr"/>
-      <c r="J123" s="3" t="n">
-        <v>81</v>
-      </c>
+      <c r="J123" s="2" t="inlineStr"/>
       <c r="K123" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="L123" s="2" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="L123" s="3" t="n">
+        <v>59</v>
+      </c>
       <c r="M123" s="3" t="n">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="N123" s="2" t="inlineStr"/>
+      <c r="O123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -4961,32 +5578,37 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Utpal Hazarika</t>
-        </is>
-      </c>
-      <c r="D124" s="3" t="n">
-        <v>78</v>
+          <t>Sourav Mahanta</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>06-06-2010</t>
+        </is>
       </c>
       <c r="E124" s="3" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="G124" s="2" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>92</v>
+      </c>
       <c r="H124" s="2" t="inlineStr"/>
       <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="3" t="n">
-        <v>53</v>
-      </c>
+      <c r="J124" s="2" t="inlineStr"/>
       <c r="K124" s="3" t="n">
         <v>52</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="M124" s="2" t="inlineStr"/>
       <c r="N124" s="2" t="inlineStr"/>
+      <c r="O124" s="3" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -4999,32 +5621,37 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Sourav Sarmah</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="n">
-        <v>43</v>
+          <t>Gitika Boro</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>08-11-2010</t>
+        </is>
       </c>
       <c r="E125" s="3" t="n">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>86</v>
-      </c>
-      <c r="G125" s="2" t="inlineStr"/>
+        <v>81</v>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>53</v>
+      </c>
       <c r="H125" s="2" t="inlineStr"/>
       <c r="I125" s="2" t="inlineStr"/>
-      <c r="J125" s="3" t="n">
-        <v>80</v>
-      </c>
+      <c r="J125" s="2" t="inlineStr"/>
       <c r="K125" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="L125" s="2" t="inlineStr"/>
-      <c r="M125" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="N125" s="2" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="L125" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="M125" s="2" t="inlineStr"/>
+      <c r="N125" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="O125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -5037,32 +5664,37 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Mintu Bhattacharya</t>
-        </is>
-      </c>
-      <c r="D126" s="3" t="n">
-        <v>91</v>
+          <t>Anaya Baruah</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>14-11-2010</t>
+        </is>
       </c>
       <c r="E126" s="3" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="G126" s="2" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>51</v>
+      </c>
       <c r="H126" s="2" t="inlineStr"/>
       <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="3" t="n">
-        <v>72</v>
-      </c>
+      <c r="J126" s="2" t="inlineStr"/>
       <c r="K126" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="L126" s="2" t="inlineStr"/>
-      <c r="M126" s="3" t="n">
-        <v>57</v>
-      </c>
-      <c r="N126" s="2" t="inlineStr"/>
+        <v>76</v>
+      </c>
+      <c r="L126" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="M126" s="2" t="inlineStr"/>
+      <c r="N126" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="O126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -5075,32 +5707,37 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Dimpi Medhi</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="n">
-        <v>53</v>
+          <t>Mamoni Kalita</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>11-12-2010</t>
+        </is>
       </c>
       <c r="E127" s="3" t="n">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="G127" s="2" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="G127" s="3" t="n">
+        <v>92</v>
+      </c>
       <c r="H127" s="2" t="inlineStr"/>
       <c r="I127" s="2" t="inlineStr"/>
-      <c r="J127" s="3" t="n">
-        <v>97</v>
-      </c>
+      <c r="J127" s="2" t="inlineStr"/>
       <c r="K127" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="L127" s="2" t="inlineStr"/>
-      <c r="M127" s="2" t="inlineStr"/>
-      <c r="N127" s="3" t="n">
-        <v>51</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="L127" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="M127" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="N127" s="2" t="inlineStr"/>
+      <c r="O127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -5113,32 +5750,37 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Kaushik Das</t>
-        </is>
-      </c>
-      <c r="D128" s="3" t="n">
-        <v>54</v>
+          <t>Kangkan Choudhury</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>25-02-2010</t>
+        </is>
       </c>
       <c r="E128" s="3" t="n">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="G128" s="2" t="inlineStr"/>
+        <v>63</v>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>93</v>
+      </c>
       <c r="H128" s="2" t="inlineStr"/>
       <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" s="3" t="n">
-        <v>42</v>
-      </c>
+      <c r="J128" s="2" t="inlineStr"/>
       <c r="K128" s="3" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="L128" s="3" t="n">
-        <v>78</v>
-      </c>
-      <c r="M128" s="2" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="M128" s="3" t="n">
+        <v>91</v>
+      </c>
       <c r="N128" s="2" t="inlineStr"/>
+      <c r="O128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -5151,32 +5793,37 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Sangita Talukdar</t>
-        </is>
-      </c>
-      <c r="D129" s="3" t="n">
-        <v>63</v>
+          <t>Barnali Kakati</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>27-09-2010</t>
+        </is>
       </c>
       <c r="E129" s="3" t="n">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="G129" s="2" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>87</v>
+      </c>
       <c r="H129" s="2" t="inlineStr"/>
       <c r="I129" s="2" t="inlineStr"/>
-      <c r="J129" s="3" t="n">
-        <v>97</v>
-      </c>
+      <c r="J129" s="2" t="inlineStr"/>
       <c r="K129" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="L129" s="2" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="L129" s="3" t="n">
+        <v>98</v>
+      </c>
       <c r="M129" s="3" t="n">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="N129" s="2" t="inlineStr"/>
+      <c r="O129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -5189,31 +5836,36 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Hirak Gogoi</t>
-        </is>
-      </c>
-      <c r="D130" s="3" t="n">
-        <v>33</v>
+          <t>Abhijit Medhi</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>25-03-2010</t>
+        </is>
       </c>
       <c r="E130" s="3" t="n">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="G130" s="2" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>74</v>
+      </c>
       <c r="H130" s="2" t="inlineStr"/>
       <c r="I130" s="2" t="inlineStr"/>
-      <c r="J130" s="3" t="n">
-        <v>27</v>
-      </c>
+      <c r="J130" s="2" t="inlineStr"/>
       <c r="K130" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="L130" s="2" t="inlineStr"/>
+        <v>81</v>
+      </c>
+      <c r="L130" s="3" t="n">
+        <v>78</v>
+      </c>
       <c r="M130" s="2" t="inlineStr"/>
-      <c r="N130" s="3" t="n">
-        <v>29</v>
+      <c r="N130" s="2" t="inlineStr"/>
+      <c r="O130" s="3" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="131">
@@ -5227,32 +5879,37 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Mintu Deka</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="n">
-        <v>86</v>
+          <t>Mintu Bhattacharya</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>25-07-2010</t>
+        </is>
       </c>
       <c r="E131" s="3" t="n">
         <v>80</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="G131" s="2" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>98</v>
+      </c>
       <c r="H131" s="2" t="inlineStr"/>
       <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="3" t="n">
-        <v>50</v>
-      </c>
+      <c r="J131" s="2" t="inlineStr"/>
       <c r="K131" s="3" t="n">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="L131" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="M131" s="2" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="M131" s="3" t="n">
+        <v>56</v>
+      </c>
       <c r="N131" s="2" t="inlineStr"/>
+      <c r="O131" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
